--- a/laudos.xlsx
+++ b/laudos.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resultados" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Amostras" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alertas" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Resultados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Amostras" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Matriz" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Alertas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Log" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resultados'!$A$1:$W$68</definedName>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="X2" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS/2026/2026-09/2026-09-30_AB_GOIABAL_4293-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_GOIABAL_4293-2026.pdf</t>
         </is>
       </c>
       <c r="Y2" s="3" t="inlineStr">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS/2026/2026-09/2026-09-30_AB_MONTANTE_4296-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_MONTANTE_4296-2026.pdf</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS/2026/2026-09/2026-09-30_AB_JUSANTE_4294-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_JUSANTE_4294-2026.pdf</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS/2026/2026-09/2026-09-30_AB_CAPTACAO_4295-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_CAPTACAO_4295-2026.pdf</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS/2026/2026-09/2026-09-30_AB_SAIDA-DA-MINA_4291-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_SAIDA-DA-MINA_4291-2026.pdf</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS/2026/2026-09/2026-09-30_AB_JUSANTE_4219-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_JUSANTE_4219-2026.pdf</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS/2026/2026-09/2026-09-30_AR_LAGOA-01_4221-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AR_LAGOA-01_4221-2026.pdf</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS/2026/2026-09/2026-09-30_AR_LAGOA-07_4220-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AR_LAGOA-07_4220-2026.pdf</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS/2026/2026-09/2026-09-30_AB_REPRESA-1_4218-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_REPRESA-1_4218-2026.pdf</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
@@ -8725,7 +8725,7 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS/2026/2026-09/2026-09-30_AB_REPRESA-1_4292-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_REPRESA-1_4292-2026.pdf</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -10063,7 +10063,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:39:02</t>
+          <t>2026-10-20 14:48:36</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -10086,14 +10086,14 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS/2026/2026-09/2026-09-30_AB_MONTANTE_4296-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_MONTANTE_4296-2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:39:02</t>
+          <t>2026-10-20 14:48:36</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -10116,14 +10116,14 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS/2026/2026-09/2026-09-30_AB_CAPTACAO_4295-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_CAPTACAO_4295-2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:39:02</t>
+          <t>2026-10-20 14:48:36</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -10146,14 +10146,14 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS/2026/2026-09/2026-09-30_AB_JUSANTE_4294-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_JUSANTE_4294-2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:39:02</t>
+          <t>2026-10-20 14:48:36</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -10176,14 +10176,14 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS/2026/2026-09/2026-09-30_AB_GOIABAL_4293-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_GOIABAL_4293-2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:39:02</t>
+          <t>2026-10-20 14:48:36</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -10206,14 +10206,14 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS/2026/2026-09/2026-09-30_AB_REPRESA-1_4292-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_REPRESA-1_4292-2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:39:02</t>
+          <t>2026-10-20 14:48:36</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -10236,14 +10236,14 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS/2026/2026-09/2026-09-30_AB_SAIDA-DA-MINA_4291-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_SAIDA-DA-MINA_4291-2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:39:02</t>
+          <t>2026-10-20 14:48:36</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -10266,14 +10266,14 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS/2026/2026-09/2026-09-30_AR_LAGOA-01_4221-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AR_LAGOA-01_4221-2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:39:02</t>
+          <t>2026-10-20 14:48:36</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -10296,14 +10296,14 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS/2026/2026-09/2026-09-30_AR_LAGOA-07_4220-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AR_LAGOA-07_4220-2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:39:02</t>
+          <t>2026-10-20 14:48:36</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -10326,14 +10326,14 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS/2026/2026-09/2026-09-30_AB_JUSANTE_4219-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_JUSANTE_4219-2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:39:02</t>
+          <t>2026-10-20 14:48:36</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS/2026/2026-09/2026-09-30_AB_REPRESA-1_4218-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_REPRESA-1_4218-2026.pdf</t>
         </is>
       </c>
     </row>

--- a/laudos.xlsx
+++ b/laudos.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resultados'!$A$1:$W$68</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Amostras'!$A$1:$Y$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Alertas'!$A$1:$G$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Log'!$A$1:$F$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Log'!$A$1:$F$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -10017,11 +10017,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -10063,30 +10063,26 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:48:36</t>
+          <t>2026-10-20 16:19:28</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>4296-1-2026_0.pdf</t>
+          <t>19813-2026 - 1-0.pdf</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Processado</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>4296-1/2026.0</t>
-        </is>
-      </c>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_MONTANTE_4296-2026.pdf</t>
+          <t>Não parece um laudo Aqualit (texto 'Relatório de Análises' não encontrado). Pode ser um PDF escaneado ou de outro laboratório. — movido para 03_ERROS</t>
         </is>
       </c>
     </row>
@@ -10098,7 +10094,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>4295-1-2026_0.pdf</t>
+          <t>4296-1-2026_0.pdf</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -10108,15 +10104,15 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>4295-1/2026.0</t>
+          <t>4296-1/2026.0</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_CAPTACAO_4295-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_MONTANTE_4296-2026.pdf</t>
         </is>
       </c>
     </row>
@@ -10128,7 +10124,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>4294-1-2026_0.pdf</t>
+          <t>4295-1-2026_0.pdf</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -10138,15 +10134,15 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>4294-1/2026.0</t>
+          <t>4295-1/2026.0</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_JUSANTE_4294-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_CAPTACAO_4295-2026.pdf</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10154,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>4293-1-2026_0.pdf</t>
+          <t>4294-1-2026_0.pdf</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -10168,7 +10164,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>4293-1/2026.0</t>
+          <t>4294-1/2026.0</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
@@ -10176,7 +10172,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_GOIABAL_4293-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_JUSANTE_4294-2026.pdf</t>
         </is>
       </c>
     </row>
@@ -10188,7 +10184,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>4292-1-2026_0.pdf</t>
+          <t>4293-1-2026_0.pdf</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -10198,7 +10194,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>4292-1/2026.0</t>
+          <t>4293-1/2026.0</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
@@ -10206,7 +10202,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_REPRESA-1_4292-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_GOIABAL_4293-2026.pdf</t>
         </is>
       </c>
     </row>
@@ -10218,7 +10214,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>4291-1-2026_0.pdf</t>
+          <t>4292-1-2026_0.pdf</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -10228,7 +10224,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>4291-1/2026.0</t>
+          <t>4292-1/2026.0</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
@@ -10236,7 +10232,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_SAIDA-DA-MINA_4291-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_REPRESA-1_4292-2026.pdf</t>
         </is>
       </c>
     </row>
@@ -10248,7 +10244,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>4221-1-2026_0.pdf</t>
+          <t>4291-1-2026_0.pdf</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -10258,15 +10254,15 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>4221-1/2026.0</t>
+          <t>4291-1/2026.0</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AR_LAGOA-01_4221-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_SAIDA-DA-MINA_4291-2026.pdf</t>
         </is>
       </c>
     </row>
@@ -10278,7 +10274,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>4220-1-2026_0.pdf</t>
+          <t>4221-1-2026_0.pdf</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -10288,7 +10284,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>4220-1/2026.0</t>
+          <t>4221-1/2026.0</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -10296,7 +10292,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AR_LAGOA-07_4220-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AR_LAGOA-01_4221-2026.pdf</t>
         </is>
       </c>
     </row>
@@ -10308,7 +10304,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>4219-1-2026_0.pdf</t>
+          <t>4220-1-2026_0.pdf</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -10318,15 +10314,15 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>4219-1/2026.0</t>
+          <t>4220-1/2026.0</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_JUSANTE_4219-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AR_LAGOA-07_4220-2026.pdf</t>
         </is>
       </c>
     </row>
@@ -10338,7 +10334,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>4218-1-2026_0.pdf</t>
+          <t>4219-1-2026_0.pdf</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -10348,7 +10344,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>4218-1/2026.0</t>
+          <t>4219-1/2026.0</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
@@ -10356,12 +10352,42 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_JUSANTE_4219-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:48:36</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>4218-1-2026_0.pdf</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Processado</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>4218-1/2026.0</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
           <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_REPRESA-1_4218-2026.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F11"/>
+  <autoFilter ref="A1:F12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/laudos.xlsx
+++ b/laudos.xlsx
@@ -14,10 +14,10 @@
     <sheet name="Log" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resultados'!$A$1:$W$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Amostras'!$A$1:$Y$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Alertas'!$A$1:$G$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Log'!$A$1:$F$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resultados'!$A$1:$W$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Amostras'!$A$1:$Y$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Alertas'!$A$1:$G$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Log'!$A$1:$F$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -114,9 +114,9 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -499,11 +499,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W68"/>
+  <dimension ref="A1:W69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -646,31 +646,31 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46295.47916666666</v>
+        <v>46259.56944444445</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Goiabal</t>
+          <t>Bomba De Captação De Efluentes - Efluente Bruto</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Água bruta</t>
+          <t>Água residual</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Goiabal</t>
+          <t>Conama 430</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>4293-1/2026.0</t>
+          <t>1081-1/2026.0</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>4293/2026.0.A</t>
+          <t>1081/2026.0.A</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -680,72 +680,68 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Físico-Químico</t>
+          <t>Efluentes</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Alumínio Dissolvido</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
+          <t>DBO5</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="4" t="n">
-        <v>0.02</v>
+        <v>879</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>mg Al/L</t>
+          <t>mg O2/L</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>&lt; 0,02 mg Al/L</t>
+          <t>879,00 mgO2/L</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>CONAMA nº 357</t>
+          <t>Resolução Nº 430 - (Seção II)</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>até 0,1 mg/L</t>
+          <t>60% de remoção mgO2/L</t>
         </is>
       </c>
       <c r="P2" s="5" t="n">
-        <v>0.02</v>
+        <v>2</v>
       </c>
       <c r="Q2" s="5" t="n">
-        <v>0.01</v>
+        <v>0.6</v>
       </c>
       <c r="R2" s="5" t="n">
-        <v>0.01</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>SMWW 3500-Al B - 24ed.</t>
+          <t>SMWW 5210B - 24ed.</t>
         </is>
       </c>
       <c r="T2" s="2" t="n">
-        <v>46308.41666666666</v>
+        <v>46262</v>
       </c>
       <c r="U2" s="6" t="inlineStr">
         <is>
           <t>Conforme</t>
         </is>
       </c>
-      <c r="V2" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
+      <c r="V2" s="7" t="inlineStr">
+        <is>
+          <t>Não verificável</t>
         </is>
       </c>
       <c r="W2" s="3" t="inlineStr">
         <is>
-          <t>d552c76bd7854cefae97a690cf7f9dd4</t>
+          <t>f6136d7c8d5043028ae926545fdfde9d</t>
         </is>
       </c>
     </row>
@@ -790,7 +786,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Cloro residual</t>
+          <t>Alumínio Dissolvido</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -799,16 +795,16 @@
         </is>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>mg Cl/L</t>
+          <t>mg Al/L</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>&lt; 0,1 mg Cl/L</t>
+          <t>&lt; 0,02 mg Al/L</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -818,34 +814,34 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>até 0,01 mg Cl/L</t>
+          <t>até 0,1 mg/L</t>
         </is>
       </c>
       <c r="P3" s="5" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="Q3" s="5" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="R3" s="5" t="n">
         <v>0.01</v>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>SMWW 4500Cl G - 24ed.</t>
+          <t>SMWW 3500-Al B - 24ed.</t>
         </is>
       </c>
       <c r="T3" s="2" t="n">
-        <v>46298.35416666666</v>
+        <v>46308.41666666666</v>
       </c>
       <c r="U3" s="6" t="inlineStr">
         <is>
           <t>Conforme</t>
         </is>
       </c>
-      <c r="V3" s="7" t="inlineStr">
-        <is>
-          <t>Indeterminado</t>
+      <c r="V3" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr">
@@ -895,21 +891,25 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Ferro dissolvido</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr"/>
+          <t>Cloro residual</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
       <c r="K4" s="4" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>mg Fe/L</t>
+          <t>mg Cl/L</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>0,06 mg Fe/L</t>
+          <t>&lt; 0,1 mg Cl/L</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -919,11 +919,11 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>até 0,3 mg Fe/L</t>
+          <t>até 0,01 mg Cl/L</t>
         </is>
       </c>
       <c r="P4" s="5" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -933,20 +933,20 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>SMWW 3500-Fe B - 24ed.</t>
+          <t>SMWW 4500Cl G - 24ed.</t>
         </is>
       </c>
       <c r="T4" s="2" t="n">
-        <v>46300.41666666666</v>
+        <v>46298.35416666666</v>
       </c>
       <c r="U4" s="6" t="inlineStr">
         <is>
           <t>Conforme</t>
         </is>
       </c>
-      <c r="V4" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>Indeterminado</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
@@ -991,26 +991,26 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Efluentes</t>
+          <t>Físico-Químico</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Oxigênio Dissolvido</t>
+          <t>Ferro dissolvido</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="4" t="n">
-        <v>7.2</v>
+        <v>0.06</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>mg O2/L</t>
+          <t>mg Fe/L</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>7,20 mg O2/L</t>
+          <t>0,06 mg Fe/L</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -1020,25 +1020,25 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>não inferior a 5,0mg/L O2 mg O2/L</t>
+          <t>até 0,3 mg Fe/L</t>
         </is>
       </c>
       <c r="P5" s="5" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>SMWW 4500O C - 24ed.</t>
+          <t>SMWW 3500-Fe B - 24ed.</t>
         </is>
       </c>
       <c r="T5" s="2" t="n">
-        <v>46297</v>
+        <v>46300.41666666666</v>
       </c>
       <c r="U5" s="6" t="inlineStr">
         <is>
@@ -1058,11 +1058,11 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46295.48611111111</v>
+        <v>46295.47916666666</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Montante</t>
+          <t>Goiabal</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1072,17 +1072,17 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Montante</t>
+          <t>Goiabal</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>4296-1/2026.0</t>
+          <t>4293-1/2026.0</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>4296/2026.0.A</t>
+          <t>4293/2026.0.A</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="4" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>7,10 mg O2/L</t>
+          <t>7,20 mg O2/L</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1153,17 +1153,17 @@
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>26c03a970cb54efab5ba85cb5e1ef425</t>
+          <t>d552c76bd7854cefae97a690cf7f9dd4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46295.48958333334</v>
+        <v>46295.48611111111</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Jusante</t>
+          <t>Montante</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1173,17 +1173,17 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Jusante</t>
+          <t>Montante</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>4294-1/2026.0</t>
+          <t>4296-1/2026.0</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>4294/2026.0.A</t>
+          <t>4296/2026.0.A</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1193,30 +1193,26 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Físico-Químico</t>
+          <t>Efluentes</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Alumínio Dissolvido</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
+          <t>Oxigênio Dissolvido</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="4" t="n">
-        <v>0.01</v>
+        <v>7.1</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>mg Al/L</t>
+          <t>mg O2/L</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>&lt; 0,01 mg Al/L</t>
+          <t>7,10 mg O2/L</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1226,25 +1222,25 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>até 0,1 mg/L</t>
+          <t>não inferior a 5,0mg/L O2 mg O2/L</t>
         </is>
       </c>
       <c r="P7" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q7" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="Q7" s="5" t="n">
-        <v>0.01</v>
-      </c>
       <c r="R7" s="5" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>SMWW 3500-Al B - 24ed.</t>
+          <t>SMWW 4500O C - 24ed.</t>
         </is>
       </c>
       <c r="T7" s="2" t="n">
-        <v>46308.41666666666</v>
+        <v>46297</v>
       </c>
       <c r="U7" s="6" t="inlineStr">
         <is>
@@ -1258,7 +1254,7 @@
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>1563178792344916a8607c4c610e5849</t>
+          <t>26c03a970cb54efab5ba85cb5e1ef425</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1299,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Cloro residual</t>
+          <t>Alumínio Dissolvido</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1312,16 +1308,16 @@
         </is>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>mg Cl/L</t>
+          <t>mg Al/L</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>&lt; 0,1 mg Cl/L</t>
+          <t>&lt; 0,01 mg Al/L</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1331,34 +1327,34 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>até 0,01 mg Cl/L</t>
+          <t>até 0,1 mg/L</t>
         </is>
       </c>
       <c r="P8" s="5" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="R8" s="5" t="n">
         <v>0.01</v>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>SMWW 4500Cl G - 24ed.</t>
+          <t>SMWW 3500-Al B - 24ed.</t>
         </is>
       </c>
       <c r="T8" s="2" t="n">
-        <v>46298.35416666666</v>
+        <v>46308.41666666666</v>
       </c>
       <c r="U8" s="6" t="inlineStr">
         <is>
           <t>Conforme</t>
         </is>
       </c>
-      <c r="V8" s="7" t="inlineStr">
-        <is>
-          <t>Indeterminado</t>
+      <c r="V8" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
@@ -1393,36 +1389,40 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>4294/2026.0</t>
+          <t>4294/2026.0.A</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Instrumental</t>
+          <t>Físico-Químico</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Cobre dissolvido</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr"/>
+          <t>Cloro residual</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
       <c r="K9" s="4" t="n">
-        <v>0.008</v>
+        <v>0.1</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>mg Cu/L</t>
+          <t>mg Cl/L</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>0,008 mgCu/L</t>
+          <t>&lt; 0,1 mg Cl/L</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1432,34 +1432,34 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>até 0,009 mg/L</t>
+          <t>até 0,01 mg Cl/L</t>
         </is>
       </c>
       <c r="P9" s="5" t="n">
-        <v>0.002</v>
+        <v>0.1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.01</v>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>SMWW 3120B - 24ed.</t>
+          <t>SMWW 4500Cl G - 24ed.</t>
         </is>
       </c>
       <c r="T9" s="2" t="n">
-        <v>46298.625</v>
+        <v>46298.35416666666</v>
       </c>
       <c r="U9" s="6" t="inlineStr">
         <is>
           <t>Conforme</t>
         </is>
       </c>
-      <c r="V9" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>Indeterminado</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
@@ -1494,36 +1494,36 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>4294/2026.0.A</t>
+          <t>4294/2026.0</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Efluentes</t>
+          <t>Instrumental</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Oxigênio Dissolvido</t>
+          <t>Cobre dissolvido</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="4" t="n">
-        <v>7</v>
+        <v>0.008</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>mg O2/L</t>
+          <t>mg Cu/L</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>7,00 mg O2/L</t>
+          <t>0,008 mgCu/L</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1533,25 +1533,25 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>não inferior a 5,0mg/L O2 mg O2/L</t>
+          <t>até 0,009 mg/L</t>
         </is>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0.05</v>
+        <v>0.002</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>0.02</v>
+        <v>0.001</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>0.02</v>
+        <v>0.0008</v>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>SMWW 4500O C - 24ed.</t>
+          <t>SMWW 3120B - 24ed.</t>
         </is>
       </c>
       <c r="T10" s="2" t="n">
-        <v>46297</v>
+        <v>46298.625</v>
       </c>
       <c r="U10" s="6" t="inlineStr">
         <is>
@@ -1571,11 +1571,11 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46295.5</v>
+        <v>46295.48958333334</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Captação</t>
+          <t>Jusante</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1585,17 +1585,17 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Captação</t>
+          <t>Jusante</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>4295-1/2026.0</t>
+          <t>4294-1/2026.0</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>4295/2026.0.A</t>
+          <t>4294/2026.0.A</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1605,30 +1605,26 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Físico-Químico</t>
+          <t>Efluentes</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Cloro residual</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
+          <t>Oxigênio Dissolvido</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="4" t="n">
-        <v>0.1</v>
+        <v>7</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>mg Cl/L</t>
+          <t>mg O2/L</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>&lt; 0,1 mg Cl/L</t>
+          <t>7,00 mg O2/L</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1638,39 +1634,39 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>até 0,01 mg Cl/L</t>
+          <t>não inferior a 5,0mg/L O2 mg O2/L</t>
         </is>
       </c>
       <c r="P11" s="5" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>SMWW 4500Cl G - 24ed.</t>
+          <t>SMWW 4500O C - 24ed.</t>
         </is>
       </c>
       <c r="T11" s="2" t="n">
-        <v>46298.35416666666</v>
+        <v>46297</v>
       </c>
       <c r="U11" s="6" t="inlineStr">
         <is>
           <t>Conforme</t>
         </is>
       </c>
-      <c r="V11" s="7" t="inlineStr">
-        <is>
-          <t>Indeterminado</t>
+      <c r="V11" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>646404d0f8884d71b4e2c86ee93ee05c</t>
+          <t>1563178792344916a8607c4c610e5849</t>
         </is>
       </c>
     </row>
@@ -1710,26 +1706,30 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Efluentes</t>
+          <t>Físico-Químico</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Oxigênio Dissolvido</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr"/>
+          <t>Cloro residual</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
       <c r="K12" s="4" t="n">
-        <v>7.4</v>
+        <v>0.1</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>mg O2/L</t>
+          <t>mg Cl/L</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>7,40 mg O2/L</t>
+          <t>&lt; 0,1 mg Cl/L</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1739,34 +1739,34 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>não inferior a 5,0mg/L O2 mg O2/L</t>
+          <t>até 0,01 mg Cl/L</t>
         </is>
       </c>
       <c r="P12" s="5" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>SMWW 4500O C - 24ed.</t>
+          <t>SMWW 4500Cl G - 24ed.</t>
         </is>
       </c>
       <c r="T12" s="2" t="n">
-        <v>46297</v>
+        <v>46298.35416666666</v>
       </c>
       <c r="U12" s="6" t="inlineStr">
         <is>
           <t>Conforme</t>
         </is>
       </c>
-      <c r="V12" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>Indeterminado</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
@@ -1777,11 +1777,11 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46295.50902777778</v>
+        <v>46295.5</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Saída da Mina</t>
+          <t>Captação</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1791,17 +1791,17 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Saída Mina</t>
+          <t>Captação</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>4291-1/2026.0</t>
+          <t>4295-1/2026.0</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>4291/2026.0.A</t>
+          <t>4295/2026.0.A</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1811,54 +1811,54 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Físico-Químico</t>
+          <t>Efluentes</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Alumínio Dissolvido</t>
+          <t>Oxigênio Dissolvido</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>mg O2/L</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>7,40 mg O2/L</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>CONAMA nº 357</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>não inferior a 5,0mg/L O2 mg O2/L</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="n">
         <v>0.05</v>
       </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>mg Al/L</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>0,05 mg Al/L</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>CONAMA nº 357</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>até 0,1 mg/L</t>
-        </is>
-      </c>
-      <c r="P13" s="5" t="n">
+      <c r="Q13" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="Q13" s="5" t="n">
-        <v>0.01</v>
-      </c>
       <c r="R13" s="5" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>SMWW 3500-Al B - 24ed.</t>
+          <t>SMWW 4500O C - 24ed.</t>
         </is>
       </c>
       <c r="T13" s="2" t="n">
-        <v>46308.41666666666</v>
+        <v>46297</v>
       </c>
       <c r="U13" s="6" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>c404d556c3a34a0382e0ecb403b34ae8</t>
+          <t>646404d0f8884d71b4e2c86ee93ee05c</t>
         </is>
       </c>
     </row>
@@ -1902,36 +1902,36 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>4291/2026.0</t>
+          <t>4291/2026.0.A</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Instrumental</t>
+          <t>Físico-Químico</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Cobre dissolvido</t>
+          <t>Alumínio Dissolvido</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="4" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>mg Cu/L</t>
+          <t>mg Al/L</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>0,009 mgCu/L</t>
+          <t>0,05 mg Al/L</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1941,25 +1941,25 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>até 0,009 mg/L</t>
+          <t>até 0,1 mg/L</t>
         </is>
       </c>
       <c r="P14" s="5" t="n">
-        <v>0.002</v>
+        <v>0.02</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>0.001</v>
+        <v>0.01</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.01</v>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>SMWW 3120B - 24ed.</t>
+          <t>SMWW 3500-Al B - 24ed.</t>
         </is>
       </c>
       <c r="T14" s="2" t="n">
-        <v>46298.625</v>
+        <v>46308.41666666666</v>
       </c>
       <c r="U14" s="6" t="inlineStr">
         <is>
@@ -2003,36 +2003,36 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>4291/2026.0.A</t>
+          <t>4291/2026.0</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Físico-Químico</t>
+          <t>Instrumental</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Ferro dissolvido</t>
+          <t>Cobre dissolvido</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr"/>
       <c r="K15" s="4" t="n">
-        <v>3.2</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>mg Fe/L</t>
+          <t>mg Cu/L</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>3,20 mg Fe/L</t>
+          <t>0,009 mgCu/L</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -2042,34 +2042,34 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>até 0,3 mg Fe/L</t>
+          <t>até 0,009 mg/L</t>
         </is>
       </c>
       <c r="P15" s="5" t="n">
-        <v>0.01</v>
+        <v>0.002</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>0.01</v>
+        <v>0.0008</v>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>SMWW 3500-Fe B - 24ed.</t>
+          <t>SMWW 3120B - 24ed.</t>
         </is>
       </c>
       <c r="T15" s="2" t="n">
-        <v>46300.41666666666</v>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
+        <v>46298.625</v>
+      </c>
+      <c r="U15" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="V15" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
@@ -2114,26 +2114,26 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Efluentes</t>
+          <t>Físico-Químico</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Oxigênio Dissolvido</t>
+          <t>Ferro dissolvido</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="4" t="n">
-        <v>7.1</v>
+        <v>3.2</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>mg O2/L</t>
+          <t>mg Fe/L</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>7,10 mg O2/L</t>
+          <t>3,20 mg Fe/L</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2143,34 +2143,34 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>não inferior a 5,0mg/L O2 mg O2/L</t>
+          <t>até 0,3 mg Fe/L</t>
         </is>
       </c>
       <c r="P16" s="5" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>SMWW 4500O C - 24ed.</t>
+          <t>SMWW 3500-Fe B - 24ed.</t>
         </is>
       </c>
       <c r="T16" s="2" t="n">
-        <v>46297</v>
-      </c>
-      <c r="U16" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
-        </is>
-      </c>
-      <c r="V16" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
+        <v>46300.41666666666</v>
+      </c>
+      <c r="U16" s="9" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="V16" s="9" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
@@ -2181,11 +2181,11 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46295.51388888889</v>
+        <v>46295.50902777778</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Jusante</t>
+          <t>Saída da Mina</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -2195,17 +2195,17 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Montante e Jusante</t>
+          <t>Saída Mina</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>4219-1/2026.0</t>
+          <t>4291-1/2026.0</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>4219/2026.0.A</t>
+          <t>4291/2026.0.A</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -2215,26 +2215,26 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Microbiológico</t>
+          <t>Efluentes</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Coliformes termotolerantes</t>
+          <t>Oxigênio Dissolvido</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr"/>
       <c r="K17" s="4" t="n">
-        <v>9000</v>
+        <v>7.1</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>NMP/100 mL</t>
+          <t>mg O2/L</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>9x10³ NMP/100 mL</t>
+          <t>7,10 mg O2/L</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -2244,39 +2244,39 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>até 1.000NMP/100mL</t>
+          <t>não inferior a 5,0mg/L O2 mg O2/L</t>
         </is>
       </c>
       <c r="P17" s="5" t="n">
-        <v>1.1</v>
+        <v>0.05</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>0.3</v>
+        <v>0.02</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>0.4</v>
+        <v>0.02</v>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>SMWW 9221B, C e E - 24ed.</t>
+          <t>SMWW 4500O C - 24ed.</t>
         </is>
       </c>
       <c r="T17" s="2" t="n">
-        <v>46296.66666666666</v>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
+        <v>46297</v>
+      </c>
+      <c r="U17" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="V17" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>ddaf07d7cbcf4dbc81240b851f9b3df3</t>
+          <t>c404d556c3a34a0382e0ecb403b34ae8</t>
         </is>
       </c>
     </row>
@@ -2316,30 +2316,26 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Físico-Químico</t>
+          <t>Microbiológico</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Cor Verdadeira</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
+          <t>Coliformes termotolerantes</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr"/>
       <c r="K18" s="4" t="n">
-        <v>0.6</v>
+        <v>9000</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>mg Pt-Co/L</t>
+          <t>NMP/100 mL</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>&lt; 0,60 mg Pt-Co/L</t>
+          <t>9x10³ NMP/100 mL</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2349,34 +2345,34 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>até 75 mg Pt-Co/L</t>
+          <t>até 1.000NMP/100mL</t>
         </is>
       </c>
       <c r="P18" s="5" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>SMWW 2120C - 24ed.</t>
+          <t>SMWW 9221B, C e E - 24ed.</t>
         </is>
       </c>
       <c r="T18" s="2" t="n">
-        <v>46300.54166666666</v>
-      </c>
-      <c r="U18" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
-        </is>
-      </c>
-      <c r="V18" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
+        <v>46296.66666666666</v>
+      </c>
+      <c r="U18" s="9" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="V18" s="9" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
@@ -2421,26 +2417,30 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Efluentes</t>
+          <t>Físico-Químico</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>DBO5</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr"/>
+          <t>Cor Verdadeira</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
       <c r="K19" s="4" t="n">
-        <v>69</v>
+        <v>0.6</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>mg O2/L</t>
+          <t>mg Pt-Co/L</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>69,00 mgO2/L</t>
+          <t>&lt; 0,60 mg Pt-Co/L</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>até 5 mgO2/L</t>
+          <t>até 75 mg Pt-Co/L</t>
         </is>
       </c>
       <c r="P19" s="5" t="n">
@@ -2460,24 +2460,24 @@
         <v>0.6</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>SMWW 5210B - 24ed.</t>
+          <t>SMWW 2120C - 24ed.</t>
         </is>
       </c>
       <c r="T19" s="2" t="n">
-        <v>46296</v>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
+        <v>46300.54166666666</v>
+      </c>
+      <c r="U19" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="V19" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
@@ -2522,17 +2522,17 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Físico-Químico</t>
+          <t>Efluentes</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>DQO</t>
+          <t>DBO5</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr"/>
       <c r="K20" s="4" t="n">
-        <v>128</v>
+        <v>69</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>128,00 mg O2/L</t>
+          <t>69,00 mgO2/L</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>até 5 mgO2/L</t>
         </is>
       </c>
       <c r="P20" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>0.37</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>MFQ 039.</t>
+          <t>SMWW 5210B - 24ed.</t>
         </is>
       </c>
       <c r="T20" s="2" t="n">
-        <v>46305.33333333334</v>
+        <v>46296</v>
       </c>
       <c r="U20" s="9" t="inlineStr">
         <is>
-          <t>Sem limite</t>
+          <t>Não conforme</t>
         </is>
       </c>
       <c r="V20" s="9" t="inlineStr">
         <is>
-          <t>Sem limite</t>
+          <t>Não conforme</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
@@ -2623,26 +2623,26 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Microbiológico</t>
+          <t>Físico-Químico</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <t>DQO</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="4" t="n">
-        <v>9000</v>
+        <v>128</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>NMP/100 mL</t>
+          <t>mg O2/L</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>9x10³ NMP/100 mL</t>
+          <t>128,00 mg O2/L</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -2656,28 +2656,28 @@
         </is>
       </c>
       <c r="P21" s="5" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>SMWW 9221B, C e F - 24ed.</t>
+          <t>MFQ 039.</t>
         </is>
       </c>
       <c r="T21" s="2" t="n">
-        <v>46296.66666666666</v>
-      </c>
-      <c r="U21" s="9" t="inlineStr">
+        <v>46305.33333333334</v>
+      </c>
+      <c r="U21" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
       </c>
-      <c r="V21" s="9" t="inlineStr">
+      <c r="V21" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
@@ -2714,36 +2714,36 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>4219/2026.0</t>
+          <t>4219/2026.0.A</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Físico-Químico</t>
+          <t>Microbiológico</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Fenóis</t>
+          <t>Escherichia coli</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr"/>
       <c r="K22" s="4" t="n">
-        <v>0.04</v>
+        <v>9000</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>mg Fenol/L</t>
+          <t>NMP/100 mL</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>0,04 mg Fenol/L</t>
+          <t>9x10³ NMP/100 mL</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -2753,34 +2753,34 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>até 0,003 mg Fenol/L</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>0.01</v>
+        <v>0.4</v>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>SMWW 5530 C - 24ed.</t>
+          <t>SMWW 9221B, C e F - 24ed.</t>
         </is>
       </c>
       <c r="T22" s="2" t="n">
-        <v>46308.35416666666</v>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
+        <v>46296.66666666666</v>
+      </c>
+      <c r="U22" s="7" t="inlineStr">
+        <is>
+          <t>Sem limite</t>
+        </is>
+      </c>
+      <c r="V22" s="7" t="inlineStr">
+        <is>
+          <t>Sem limite</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
@@ -2815,36 +2815,36 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>4219/2026.0.A</t>
+          <t>4219/2026.0</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Efluentes</t>
+          <t>Físico-Químico</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Oxigênio Dissolvido</t>
+          <t>Fenóis</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr"/>
       <c r="K23" s="4" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>mg O2/L</t>
+          <t>mg Fenol/L</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>0,10 mg O2/L</t>
+          <t>0,04 mg Fenol/L</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -2854,32 +2854,32 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>não inferior a 5,0mg/L O2 mg O2/L</t>
+          <t>até 0,003 mg Fenol/L</t>
         </is>
       </c>
       <c r="P23" s="5" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>SMWW 4500O C - 24ed.</t>
+          <t>SMWW 5530 C - 24ed.</t>
         </is>
       </c>
       <c r="T23" s="2" t="n">
-        <v>46296</v>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
+        <v>46308.35416666666</v>
+      </c>
+      <c r="U23" s="9" t="inlineStr">
         <is>
           <t>Não conforme</t>
         </is>
       </c>
-      <c r="V23" s="8" t="inlineStr">
+      <c r="V23" s="9" t="inlineStr">
         <is>
           <t>Não conforme</t>
         </is>
@@ -2926,26 +2926,26 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Físico-Químico</t>
+          <t>Efluentes</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Turbidez</t>
+          <t>Oxigênio Dissolvido</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr"/>
       <c r="K24" s="4" t="n">
-        <v>3.78</v>
+        <v>0.1</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>NTU</t>
+          <t>mg O2/L</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>3,78 NTU</t>
+          <t>0,10 mg O2/L</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -2955,34 +2955,34 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>até 100 NTU</t>
+          <t>não inferior a 5,0mg/L O2 mg O2/L</t>
         </is>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>0.25</v>
+        <v>0.02</v>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>SMWW 2130B - 24ed.</t>
+          <t>SMWW 4500O C - 24ed.</t>
         </is>
       </c>
       <c r="T24" s="2" t="n">
-        <v>46297</v>
-      </c>
-      <c r="U24" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
-        </is>
-      </c>
-      <c r="V24" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
+        <v>46296</v>
+      </c>
+      <c r="U24" s="9" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="V24" s="9" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
@@ -3032,17 +3032,21 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>Turbidez</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr"/>
       <c r="K25" s="4" t="n">
-        <v>6.82</v>
-      </c>
-      <c r="L25" s="3" t="inlineStr"/>
+        <v>3.78</v>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>NTU</t>
+        </is>
+      </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>6,82 NA</t>
+          <t>3,78 NTU</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -3052,23 +3056,25 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>Entre 6 e 9. NA</t>
+          <t>até 100 NTU</t>
         </is>
       </c>
       <c r="P25" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q25" s="5" t="n"/>
+        <v>0.5</v>
+      </c>
+      <c r="Q25" s="5" t="n">
+        <v>0.1</v>
+      </c>
       <c r="R25" s="5" t="n">
-        <v>0.03</v>
+        <v>0.25</v>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>SMWW 4500H+ B - 24ed.</t>
+          <t>SMWW 2130B - 24ed.</t>
         </is>
       </c>
       <c r="T25" s="2" t="n">
-        <v>46296.66666666666</v>
+        <v>46297</v>
       </c>
       <c r="U25" s="6" t="inlineStr">
         <is>
@@ -3127,25 +3133,17 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Óleos e Graxas Totais</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr"/>
       <c r="K26" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>mg Óleos e Graxas/L</t>
-        </is>
-      </c>
+        <v>6.82</v>
+      </c>
+      <c r="L26" s="3" t="inlineStr"/>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>&lt; 10,00 mg Óleos e Graxas/L</t>
+          <t>6,82 NA</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -3155,34 +3153,32 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>Virtualmente ausente</t>
+          <t>Entre 6 e 9. NA</t>
         </is>
       </c>
       <c r="P26" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q26" s="5" t="n">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="Q26" s="5" t="n"/>
       <c r="R26" s="5" t="n">
-        <v>0.8</v>
+        <v>0.03</v>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>SMWW 5520 D - 24ed.</t>
+          <t>SMWW 4500H+ B - 24ed.</t>
         </is>
       </c>
       <c r="T26" s="2" t="n">
-        <v>46308.41666666666</v>
+        <v>46296.66666666666</v>
       </c>
       <c r="U26" s="6" t="inlineStr">
         <is>
           <t>Conforme</t>
         </is>
       </c>
-      <c r="V26" s="9" t="inlineStr">
-        <is>
-          <t>Não verificável</t>
+      <c r="V26" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
@@ -3193,31 +3189,31 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46295.59027777778</v>
+        <v>46295.51388888889</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Lagoa 01</t>
+          <t>Jusante</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Água residual</t>
+          <t>Água bruta</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Montante e Jusante</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>4221-1/2026.0</t>
+          <t>4219-1/2026.0</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>4221/2026.0.A</t>
+          <t>4219/2026.0.A</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -3227,68 +3223,72 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Efluentes</t>
+          <t>Físico-Químico</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Alcalinidade total</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr"/>
+          <t>Óleos e Graxas Totais</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
       <c r="K27" s="4" t="n">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>mg CaCO3/L</t>
+          <t>mg Óleos e Graxas/L</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>56,00 mgCaCO3/L</t>
+          <t>&lt; 10,00 mg Óleos e Graxas/L</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>Resolução Nº 430 - (Seção II)</t>
+          <t>CONAMA nº 357</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Virtualmente ausente</t>
         </is>
       </c>
       <c r="P27" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="R27" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t>SMWW 2320B - 24ed.</t>
+          <t>SMWW 5520 D - 24ed.</t>
         </is>
       </c>
       <c r="T27" s="2" t="n">
-        <v>46301</v>
-      </c>
-      <c r="U27" s="9" t="inlineStr">
-        <is>
-          <t>Sem limite</t>
-        </is>
-      </c>
-      <c r="V27" s="9" t="inlineStr">
-        <is>
-          <t>Sem limite</t>
+        <v>46308.41666666666</v>
+      </c>
+      <c r="U27" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="V27" s="7" t="inlineStr">
+        <is>
+          <t>Não verificável</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>866cb8e68ec148f2a374c988ec5f44ed</t>
+          <t>ddaf07d7cbcf4dbc81240b851f9b3df3</t>
         </is>
       </c>
     </row>
@@ -3318,12 +3318,12 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>4221/2026.0</t>
+          <t>4221/2026.0.A</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -3333,21 +3333,21 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Amônia</t>
+          <t>Alcalinidade total</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr"/>
       <c r="K28" s="4" t="n">
-        <v>6.81</v>
+        <v>56</v>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>NH3</t>
+          <t>mg CaCO3/L</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>6,81 NH3</t>
+          <t>56,00 mgCaCO3/L</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -3361,28 +3361,28 @@
         </is>
       </c>
       <c r="P28" s="5" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="R28" s="5" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>SMWW 4500 NH3 F - 24ed.</t>
+          <t>SMWW 2320B - 24ed.</t>
         </is>
       </c>
       <c r="T28" s="2" t="n">
-        <v>46300</v>
-      </c>
-      <c r="U28" s="9" t="inlineStr">
+        <v>46301</v>
+      </c>
+      <c r="U28" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
       </c>
-      <c r="V28" s="9" t="inlineStr">
+      <c r="V28" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
@@ -3419,12 +3419,12 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>4221/2026.0.A</t>
+          <t>4221/2026.0</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -3434,21 +3434,21 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Condutividade</t>
+          <t>Amônia</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr"/>
       <c r="K29" s="4" t="n">
-        <v>405</v>
+        <v>6.81</v>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>µS/cm</t>
+          <t>NH3</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>405,00 µS/cm</t>
+          <t>6,81 NH3</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -3462,28 +3462,28 @@
         </is>
       </c>
       <c r="P29" s="5" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>0.03</v>
+        <v>0.18</v>
       </c>
       <c r="R29" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>SMWW 2510B - 24ed.</t>
+          <t>SMWW 4500 NH3 F - 24ed.</t>
         </is>
       </c>
       <c r="T29" s="2" t="n">
         <v>46300</v>
       </c>
-      <c r="U29" s="9" t="inlineStr">
+      <c r="U29" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
       </c>
-      <c r="V29" s="9" t="inlineStr">
+      <c r="V29" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
@@ -3535,21 +3535,21 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>DBO5</t>
+          <t>Condutividade</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr"/>
       <c r="K30" s="4" t="n">
-        <v>504.71</v>
+        <v>405</v>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>mg O2/L</t>
+          <t>µS/cm</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>504,71 mgO2/L</t>
+          <t>405,00 µS/cm</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -3559,34 +3559,34 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>60% de remoção mgO2/L</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P30" s="5" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>0.6</v>
+        <v>0.03</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t>SMWW 5210B - 24ed.</t>
+          <t>SMWW 2510B - 24ed.</t>
         </is>
       </c>
       <c r="T30" s="2" t="n">
-        <v>46296</v>
-      </c>
-      <c r="U30" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
-        </is>
-      </c>
-      <c r="V30" s="9" t="inlineStr">
-        <is>
-          <t>Não verificável</t>
+        <v>46300</v>
+      </c>
+      <c r="U30" s="7" t="inlineStr">
+        <is>
+          <t>Sem limite</t>
+        </is>
+      </c>
+      <c r="V30" s="7" t="inlineStr">
+        <is>
+          <t>Sem limite</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
@@ -3636,12 +3636,12 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>DQO</t>
+          <t>DBO5</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr"/>
       <c r="K31" s="4" t="n">
-        <v>1394</v>
+        <v>504.71</v>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1394,00 mg O2/L</t>
+          <t>504,71 mgO2/L</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -3660,34 +3660,34 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>60% de remoção mgO2/L</t>
         </is>
       </c>
       <c r="P31" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="R31" s="5" t="n">
-        <v>0.37</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>MFQ 039.</t>
+          <t>SMWW 5210B - 24ed.</t>
         </is>
       </c>
       <c r="T31" s="2" t="n">
-        <v>46300</v>
-      </c>
-      <c r="U31" s="9" t="inlineStr">
-        <is>
-          <t>Sem limite</t>
-        </is>
-      </c>
-      <c r="V31" s="9" t="inlineStr">
-        <is>
-          <t>Sem limite</t>
+        <v>46296</v>
+      </c>
+      <c r="U31" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="V31" s="7" t="inlineStr">
+        <is>
+          <t>Não verificável</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>4221/2026.0</t>
+          <t>4221/2026.0.A</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -3737,25 +3737,21 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Fenóis</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
+          <t>DQO</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr"/>
       <c r="K32" s="4" t="n">
-        <v>0</v>
+        <v>1394</v>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>mg Fenol/L</t>
+          <t>mg O2/L</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>&lt; 0,00 mg Fenol/L</t>
+          <t>1394,00 mg O2/L</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -3765,34 +3761,34 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>até 0,5 mg Fenol/L</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P32" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q32" s="5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R32" s="5" t="n">
-        <v>0.01</v>
+        <v>0.37</v>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>SMWW 5530 C - 24ed.</t>
+          <t>MFQ 039.</t>
         </is>
       </c>
       <c r="T32" s="2" t="n">
-        <v>46302</v>
-      </c>
-      <c r="U32" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
-        </is>
-      </c>
-      <c r="V32" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
+        <v>46300</v>
+      </c>
+      <c r="U32" s="7" t="inlineStr">
+        <is>
+          <t>Sem limite</t>
+        </is>
+      </c>
+      <c r="V32" s="7" t="inlineStr">
+        <is>
+          <t>Sem limite</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
@@ -3827,12 +3823,12 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>4221/2026.0.A</t>
+          <t>4221/2026.0</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -3842,21 +3838,25 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Fósforo Total</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr"/>
+          <t>Fenóis</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
       <c r="K33" s="4" t="n">
-        <v>11.06</v>
+        <v>0</v>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>mg P/L</t>
+          <t>mg Fenol/L</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>11,06 mg P/L</t>
+          <t>&lt; 0,00 mg Fenol/L</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -3866,34 +3866,34 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>até 0,5 mg Fenol/L</t>
         </is>
       </c>
       <c r="P33" s="5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="R33" s="5" t="n">
-        <v>0.14</v>
+        <v>0.01</v>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>SMWW 4500P B e C - 24ed.</t>
+          <t>SMWW 5530 C - 24ed.</t>
         </is>
       </c>
       <c r="T33" s="2" t="n">
-        <v>46303</v>
-      </c>
-      <c r="U33" s="9" t="inlineStr">
-        <is>
-          <t>Sem limite</t>
-        </is>
-      </c>
-      <c r="V33" s="9" t="inlineStr">
-        <is>
-          <t>Sem limite</t>
+        <v>46302</v>
+      </c>
+      <c r="U33" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="V33" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
@@ -3943,21 +3943,21 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>Nitrogênio Kjeldahl Total</t>
+          <t>Fósforo Total</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr"/>
       <c r="K34" s="4" t="n">
-        <v>14</v>
+        <v>11.06</v>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>mg NKT/L</t>
+          <t>mg P/L</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>14,00 mgNKT/L</t>
+          <t>11,06 mg P/L</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -3971,28 +3971,28 @@
         </is>
       </c>
       <c r="P34" s="5" t="n">
-        <v>4</v>
+        <v>0.2</v>
       </c>
       <c r="Q34" s="5" t="n">
-        <v>1.2</v>
+        <v>0.06</v>
       </c>
       <c r="R34" s="5" t="n">
-        <v>0.04</v>
+        <v>0.14</v>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t>SMWW 4500Norg C - 24ed.</t>
+          <t>SMWW 4500P B e C - 24ed.</t>
         </is>
       </c>
       <c r="T34" s="2" t="n">
-        <v>46300</v>
-      </c>
-      <c r="U34" s="9" t="inlineStr">
+        <v>46303</v>
+      </c>
+      <c r="U34" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
       </c>
-      <c r="V34" s="9" t="inlineStr">
+      <c r="V34" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
@@ -4044,25 +4044,21 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Oxigênio Dissolvido</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
+          <t>Nitrogênio Kjeldahl Total</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr"/>
       <c r="K35" s="4" t="n">
-        <v>0.02</v>
+        <v>14</v>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>mg O2/L</t>
+          <t>mg NKT/L</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>&lt; 0,02 mg O2/L</t>
+          <t>14,00 mgNKT/L</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
@@ -4076,28 +4072,28 @@
         </is>
       </c>
       <c r="P35" s="5" t="n">
-        <v>0.05</v>
+        <v>4</v>
       </c>
       <c r="Q35" s="5" t="n">
-        <v>0.02</v>
+        <v>1.2</v>
       </c>
       <c r="R35" s="5" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>SMWW 4500O C - 24ed.</t>
+          <t>SMWW 4500Norg C - 24ed.</t>
         </is>
       </c>
       <c r="T35" s="2" t="n">
-        <v>46296</v>
-      </c>
-      <c r="U35" s="9" t="inlineStr">
+        <v>46300</v>
+      </c>
+      <c r="U35" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
       </c>
-      <c r="V35" s="9" t="inlineStr">
+      <c r="V35" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
@@ -4149,21 +4145,25 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>Sólidos Dissolvidos totais</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr"/>
+          <t>Oxigênio Dissolvido</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
       <c r="K36" s="4" t="n">
-        <v>103</v>
+        <v>0.02</v>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>mg/L</t>
+          <t>mg O2/L</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>103,0000 mg/L</t>
+          <t>&lt; 0,02 mg O2/L</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -4177,28 +4177,28 @@
         </is>
       </c>
       <c r="P36" s="5" t="n">
-        <v>2.5</v>
+        <v>0.05</v>
       </c>
       <c r="Q36" s="5" t="n">
-        <v>0.75</v>
+        <v>0.02</v>
       </c>
       <c r="R36" s="5" t="n">
-        <v>0.77</v>
+        <v>0.02</v>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t>SMWW 2540C - 24ed.</t>
+          <t>SMWW 4500O C - 24ed.</t>
         </is>
       </c>
       <c r="T36" s="2" t="n">
-        <v>46303</v>
-      </c>
-      <c r="U36" s="9" t="inlineStr">
+        <v>46296</v>
+      </c>
+      <c r="U36" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
       </c>
-      <c r="V36" s="9" t="inlineStr">
+      <c r="V36" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
@@ -4250,12 +4250,12 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Sólidos Suspensos Totais</t>
+          <t>Sólidos Dissolvidos totais</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr"/>
       <c r="K37" s="4" t="n">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>50,00 mg/L</t>
+          <t>103,0000 mg/L</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -4284,22 +4284,22 @@
         <v>0.75</v>
       </c>
       <c r="R37" s="5" t="n">
-        <v>0.02</v>
+        <v>0.77</v>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>SMWW 2540D - 24ed.</t>
+          <t>SMWW 2540C - 24ed.</t>
         </is>
       </c>
       <c r="T37" s="2" t="n">
-        <v>46302</v>
-      </c>
-      <c r="U37" s="9" t="inlineStr">
+        <v>46303</v>
+      </c>
+      <c r="U37" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
       </c>
-      <c r="V37" s="9" t="inlineStr">
+      <c r="V37" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
@@ -4351,12 +4351,12 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>Sólidos Suspensos Voláteis</t>
+          <t>Sólidos Suspensos Totais</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr"/>
       <c r="K38" s="4" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>38,00 mg/L</t>
+          <t>50,00 mg/L</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -4389,18 +4389,18 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>SMWW 2540E - 24ed.</t>
+          <t>SMWW 2540D - 24ed.</t>
         </is>
       </c>
       <c r="T38" s="2" t="n">
         <v>46302</v>
       </c>
-      <c r="U38" s="9" t="inlineStr">
+      <c r="U38" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
       </c>
-      <c r="V38" s="9" t="inlineStr">
+      <c r="V38" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
@@ -4452,17 +4452,21 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>Sólidos Suspensos Voláteis</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr"/>
       <c r="K39" s="4" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="L39" s="3" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>5,26 NA</t>
+          <t>38,00 mg/L</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -4472,32 +4476,34 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>entre 5,0 a 9,0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P39" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q39" s="5" t="n"/>
+        <v>2.5</v>
+      </c>
+      <c r="Q39" s="5" t="n">
+        <v>0.75</v>
+      </c>
       <c r="R39" s="5" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>SMWW 4500H+ B - 24ed.</t>
+          <t>SMWW 2540E - 24ed.</t>
         </is>
       </c>
       <c r="T39" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="U39" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
-        </is>
-      </c>
-      <c r="V39" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
+        <v>46302</v>
+      </c>
+      <c r="U39" s="7" t="inlineStr">
+        <is>
+          <t>Sem limite</t>
+        </is>
+      </c>
+      <c r="V39" s="7" t="inlineStr">
+        <is>
+          <t>Sem limite</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
@@ -4547,21 +4553,17 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>Óleos e Graxas Totais</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr"/>
       <c r="K40" s="4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>mg Óleos e Graxas/L</t>
-        </is>
-      </c>
+        <v>5.26</v>
+      </c>
+      <c r="L40" s="3" t="inlineStr"/>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>19,50 mg Óleos e Graxas/L</t>
+          <t>5,26 NA</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -4571,34 +4573,32 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>entre 5,0 a 9,0</t>
         </is>
       </c>
       <c r="P40" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q40" s="5" t="n">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="Q40" s="5" t="n"/>
       <c r="R40" s="5" t="n">
-        <v>0.8</v>
+        <v>0.03</v>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>SMWW 5520 D - 24ed.</t>
+          <t>SMWW 4500H+ B - 24ed.</t>
         </is>
       </c>
       <c r="T40" s="2" t="n">
-        <v>46301</v>
-      </c>
-      <c r="U40" s="9" t="inlineStr">
-        <is>
-          <t>Sem limite</t>
-        </is>
-      </c>
-      <c r="V40" s="9" t="inlineStr">
-        <is>
-          <t>Sem limite</t>
+        <v>46266</v>
+      </c>
+      <c r="U40" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="V40" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
@@ -4609,11 +4609,11 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46295.59722222222</v>
+        <v>46295.59027777778</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Lagoa 07</t>
+          <t>Lagoa 01</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>4220-1/2026.0</t>
+          <t>4221-1/2026.0</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>4220/2026.0.A</t>
+          <t>4221/2026.0.A</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -4648,21 +4648,21 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Alcalinidade total</t>
+          <t>Óleos e Graxas Totais</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr"/>
       <c r="K41" s="4" t="n">
-        <v>88</v>
+        <v>19.5</v>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>mg CaCO3/L</t>
+          <t>mg Óleos e Graxas/L</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>88,00 mgCaCO3/L</t>
+          <t>19,50 mg Óleos e Graxas/L</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
@@ -4676,35 +4676,35 @@
         </is>
       </c>
       <c r="P41" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q41" s="5" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="R41" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t>SMWW 2320B - 24ed.</t>
+          <t>SMWW 5520 D - 24ed.</t>
         </is>
       </c>
       <c r="T41" s="2" t="n">
         <v>46301</v>
       </c>
-      <c r="U41" s="9" t="inlineStr">
+      <c r="U41" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
       </c>
-      <c r="V41" s="9" t="inlineStr">
+      <c r="V41" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>0634173a6d474a8c80b9a2b1502c7510</t>
+          <t>866cb8e68ec148f2a374c988ec5f44ed</t>
         </is>
       </c>
     </row>
@@ -4734,12 +4734,12 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>4220/2026.0</t>
+          <t>4220/2026.0.A</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -4749,21 +4749,21 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>Amônia</t>
+          <t>Alcalinidade total</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr"/>
       <c r="K42" s="4" t="n">
-        <v>6.81</v>
+        <v>88</v>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>NH3</t>
+          <t>mg CaCO3/L</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>6,81 NH3</t>
+          <t>88,00 mgCaCO3/L</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -4777,28 +4777,28 @@
         </is>
       </c>
       <c r="P42" s="5" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="Q42" s="5" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="R42" s="5" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t>SMWW 4500 NH3 F - 24ed.</t>
+          <t>SMWW 2320B - 24ed.</t>
         </is>
       </c>
       <c r="T42" s="2" t="n">
-        <v>46300</v>
-      </c>
-      <c r="U42" s="9" t="inlineStr">
+        <v>46301</v>
+      </c>
+      <c r="U42" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
       </c>
-      <c r="V42" s="9" t="inlineStr">
+      <c r="V42" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
@@ -4835,12 +4835,12 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>4220/2026.0.A</t>
+          <t>4220/2026.0</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
@@ -4850,21 +4850,21 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Condutividade</t>
+          <t>Amônia</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr"/>
       <c r="K43" s="4" t="n">
-        <v>457</v>
+        <v>6.81</v>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>µS/cm</t>
+          <t>NH3</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>457,00 µS/cm</t>
+          <t>6,81 NH3</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -4878,28 +4878,28 @@
         </is>
       </c>
       <c r="P43" s="5" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="Q43" s="5" t="n">
-        <v>0.03</v>
+        <v>0.18</v>
       </c>
       <c r="R43" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t>SMWW 2510B - 24ed.</t>
+          <t>SMWW 4500 NH3 F - 24ed.</t>
         </is>
       </c>
       <c r="T43" s="2" t="n">
         <v>46300</v>
       </c>
-      <c r="U43" s="9" t="inlineStr">
+      <c r="U43" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
       </c>
-      <c r="V43" s="9" t="inlineStr">
+      <c r="V43" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
@@ -4951,21 +4951,21 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>DBO5</t>
+          <t>Condutividade</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr"/>
       <c r="K44" s="4" t="n">
-        <v>382.5</v>
+        <v>457</v>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>mg O2/L</t>
+          <t>µS/cm</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>382,50 mgO2/L</t>
+          <t>457,00 µS/cm</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -4975,34 +4975,34 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>60% de remoção mgO2/L</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P44" s="5" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="Q44" s="5" t="n">
-        <v>0.6</v>
+        <v>0.03</v>
       </c>
       <c r="R44" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t>SMWW 5210B - 24ed.</t>
+          <t>SMWW 2510B - 24ed.</t>
         </is>
       </c>
       <c r="T44" s="2" t="n">
-        <v>46296</v>
-      </c>
-      <c r="U44" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
-        </is>
-      </c>
-      <c r="V44" s="9" t="inlineStr">
-        <is>
-          <t>Não verificável</t>
+        <v>46300</v>
+      </c>
+      <c r="U44" s="7" t="inlineStr">
+        <is>
+          <t>Sem limite</t>
+        </is>
+      </c>
+      <c r="V44" s="7" t="inlineStr">
+        <is>
+          <t>Sem limite</t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>DQO</t>
+          <t>DBO5</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr"/>
       <c r="K45" s="4" t="n">
-        <v>1060</v>
+        <v>382.5</v>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1060,00 mg O2/L</t>
+          <t>382,50 mgO2/L</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -5076,34 +5076,34 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>60% de remoção mgO2/L</t>
         </is>
       </c>
       <c r="P45" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q45" s="5" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="R45" s="5" t="n">
-        <v>0.37</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>MFQ 039.</t>
+          <t>SMWW 5210B - 24ed.</t>
         </is>
       </c>
       <c r="T45" s="2" t="n">
-        <v>46300</v>
-      </c>
-      <c r="U45" s="9" t="inlineStr">
-        <is>
-          <t>Sem limite</t>
-        </is>
-      </c>
-      <c r="V45" s="9" t="inlineStr">
-        <is>
-          <t>Sem limite</t>
+        <v>46296</v>
+      </c>
+      <c r="U45" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="V45" s="7" t="inlineStr">
+        <is>
+          <t>Não verificável</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>4220/2026.0</t>
+          <t>4220/2026.0.A</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -5153,21 +5153,21 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>Fenóis</t>
+          <t>DQO</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr"/>
       <c r="K46" s="4" t="n">
-        <v>0.14</v>
+        <v>1060</v>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>mg Fenol/L</t>
+          <t>mg O2/L</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>0,14 mg Fenol/L</t>
+          <t>1060,00 mg O2/L</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -5177,34 +5177,34 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>até 0,5 mg Fenol/L</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P46" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q46" s="5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R46" s="5" t="n">
-        <v>0.01</v>
+        <v>0.37</v>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t>SMWW 5530 C - 24ed.</t>
+          <t>MFQ 039.</t>
         </is>
       </c>
       <c r="T46" s="2" t="n">
-        <v>46302</v>
-      </c>
-      <c r="U46" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
-        </is>
-      </c>
-      <c r="V46" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
+        <v>46300</v>
+      </c>
+      <c r="U46" s="7" t="inlineStr">
+        <is>
+          <t>Sem limite</t>
+        </is>
+      </c>
+      <c r="V46" s="7" t="inlineStr">
+        <is>
+          <t>Sem limite</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>4220/2026.0.A</t>
+          <t>4220/2026.0</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
@@ -5254,21 +5254,21 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>Fósforo Total</t>
+          <t>Fenóis</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr"/>
       <c r="K47" s="4" t="n">
-        <v>7.25</v>
+        <v>0.14</v>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>mg P/L</t>
+          <t>mg Fenol/L</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>7,25 mg P/L</t>
+          <t>0,14 mg Fenol/L</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
@@ -5278,34 +5278,34 @@
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>até 0,5 mg Fenol/L</t>
         </is>
       </c>
       <c r="P47" s="5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="5" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="R47" s="5" t="n">
-        <v>0.14</v>
+        <v>0.01</v>
       </c>
       <c r="S47" s="3" t="inlineStr">
         <is>
-          <t>SMWW 4500P B e C - 24ed.</t>
+          <t>SMWW 5530 C - 24ed.</t>
         </is>
       </c>
       <c r="T47" s="2" t="n">
-        <v>46303</v>
-      </c>
-      <c r="U47" s="9" t="inlineStr">
-        <is>
-          <t>Sem limite</t>
-        </is>
-      </c>
-      <c r="V47" s="9" t="inlineStr">
-        <is>
-          <t>Sem limite</t>
+        <v>46302</v>
+      </c>
+      <c r="U47" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="V47" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="W47" s="3" t="inlineStr">
@@ -5355,21 +5355,21 @@
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>Nitrogênio Kjeldahl Total</t>
+          <t>Fósforo Total</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr"/>
       <c r="K48" s="4" t="n">
-        <v>14</v>
+        <v>7.25</v>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>mg NKT/L</t>
+          <t>mg P/L</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>14,00 mgNKT/L</t>
+          <t>7,25 mg P/L</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
@@ -5383,28 +5383,28 @@
         </is>
       </c>
       <c r="P48" s="5" t="n">
-        <v>4</v>
+        <v>0.2</v>
       </c>
       <c r="Q48" s="5" t="n">
-        <v>1.2</v>
+        <v>0.06</v>
       </c>
       <c r="R48" s="5" t="n">
-        <v>0.04</v>
+        <v>0.14</v>
       </c>
       <c r="S48" s="3" t="inlineStr">
         <is>
-          <t>SMWW 4500Norg C - 24ed.</t>
+          <t>SMWW 4500P B e C - 24ed.</t>
         </is>
       </c>
       <c r="T48" s="2" t="n">
-        <v>46300</v>
-      </c>
-      <c r="U48" s="9" t="inlineStr">
+        <v>46303</v>
+      </c>
+      <c r="U48" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
       </c>
-      <c r="V48" s="9" t="inlineStr">
+      <c r="V48" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
@@ -5456,25 +5456,21 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Oxigênio Dissolvido</t>
-        </is>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
+          <t>Nitrogênio Kjeldahl Total</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr"/>
       <c r="K49" s="4" t="n">
-        <v>0.02</v>
+        <v>14</v>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>mg O2/L</t>
+          <t>mg NKT/L</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>&lt; 0,02 mg O2/L</t>
+          <t>14,00 mgNKT/L</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
@@ -5488,28 +5484,28 @@
         </is>
       </c>
       <c r="P49" s="5" t="n">
-        <v>0.05</v>
+        <v>4</v>
       </c>
       <c r="Q49" s="5" t="n">
-        <v>0.02</v>
+        <v>1.2</v>
       </c>
       <c r="R49" s="5" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="S49" s="3" t="inlineStr">
         <is>
-          <t>SMWW 4500O C - 24ed.</t>
+          <t>SMWW 4500Norg C - 24ed.</t>
         </is>
       </c>
       <c r="T49" s="2" t="n">
-        <v>46296</v>
-      </c>
-      <c r="U49" s="9" t="inlineStr">
+        <v>46300</v>
+      </c>
+      <c r="U49" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
       </c>
-      <c r="V49" s="9" t="inlineStr">
+      <c r="V49" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
@@ -5561,21 +5557,25 @@
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>Sólidos Dissolvidos totais</t>
-        </is>
-      </c>
-      <c r="J50" s="3" t="inlineStr"/>
+          <t>Oxigênio Dissolvido</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
       <c r="K50" s="4" t="n">
-        <v>215</v>
+        <v>0.02</v>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>mg/L</t>
+          <t>mg O2/L</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>215,0000 mg/L</t>
+          <t>&lt; 0,02 mg O2/L</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
@@ -5589,28 +5589,28 @@
         </is>
       </c>
       <c r="P50" s="5" t="n">
-        <v>2.5</v>
+        <v>0.05</v>
       </c>
       <c r="Q50" s="5" t="n">
-        <v>0.75</v>
+        <v>0.02</v>
       </c>
       <c r="R50" s="5" t="n">
-        <v>0.77</v>
+        <v>0.02</v>
       </c>
       <c r="S50" s="3" t="inlineStr">
         <is>
-          <t>SMWW 2540C - 24ed.</t>
+          <t>SMWW 4500O C - 24ed.</t>
         </is>
       </c>
       <c r="T50" s="2" t="n">
-        <v>46303</v>
-      </c>
-      <c r="U50" s="9" t="inlineStr">
+        <v>46296</v>
+      </c>
+      <c r="U50" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
       </c>
-      <c r="V50" s="9" t="inlineStr">
+      <c r="V50" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
@@ -5662,12 +5662,12 @@
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>Sólidos Suspensos Totais</t>
+          <t>Sólidos Dissolvidos totais</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr"/>
       <c r="K51" s="4" t="n">
-        <v>138</v>
+        <v>215</v>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>138,00 mg/L</t>
+          <t>215,0000 mg/L</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
@@ -5696,22 +5696,22 @@
         <v>0.75</v>
       </c>
       <c r="R51" s="5" t="n">
-        <v>0.02</v>
+        <v>0.77</v>
       </c>
       <c r="S51" s="3" t="inlineStr">
         <is>
-          <t>SMWW 2540D - 24ed.</t>
+          <t>SMWW 2540C - 24ed.</t>
         </is>
       </c>
       <c r="T51" s="2" t="n">
-        <v>46302</v>
-      </c>
-      <c r="U51" s="9" t="inlineStr">
+        <v>46303</v>
+      </c>
+      <c r="U51" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
       </c>
-      <c r="V51" s="9" t="inlineStr">
+      <c r="V51" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
@@ -5763,12 +5763,12 @@
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>Sólidos Suspensos Voláteis</t>
+          <t>Sólidos Suspensos Totais</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr"/>
       <c r="K52" s="4" t="n">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>102,00 mg/L</t>
+          <t>138,00 mg/L</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -5801,18 +5801,18 @@
       </c>
       <c r="S52" s="3" t="inlineStr">
         <is>
-          <t>SMWW 2540E - 24ed.</t>
+          <t>SMWW 2540D - 24ed.</t>
         </is>
       </c>
       <c r="T52" s="2" t="n">
         <v>46302</v>
       </c>
-      <c r="U52" s="9" t="inlineStr">
+      <c r="U52" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
       </c>
-      <c r="V52" s="9" t="inlineStr">
+      <c r="V52" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
@@ -5864,17 +5864,21 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>Sólidos Suspensos Voláteis</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr"/>
       <c r="K53" s="4" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="L53" s="3" t="inlineStr"/>
+        <v>102</v>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>5,37 NA</t>
+          <t>102,00 mg/L</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -5884,32 +5888,34 @@
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>entre 5,0 a 9,0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P53" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q53" s="5" t="n"/>
+        <v>2.5</v>
+      </c>
+      <c r="Q53" s="5" t="n">
+        <v>0.75</v>
+      </c>
       <c r="R53" s="5" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="S53" s="3" t="inlineStr">
         <is>
-          <t>SMWW 4500H+ B - 24ed.</t>
+          <t>SMWW 2540E - 24ed.</t>
         </is>
       </c>
       <c r="T53" s="2" t="n">
-        <v>46266</v>
-      </c>
-      <c r="U53" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
-        </is>
-      </c>
-      <c r="V53" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
+        <v>46302</v>
+      </c>
+      <c r="U53" s="7" t="inlineStr">
+        <is>
+          <t>Sem limite</t>
+        </is>
+      </c>
+      <c r="V53" s="7" t="inlineStr">
+        <is>
+          <t>Sem limite</t>
         </is>
       </c>
       <c r="W53" s="3" t="inlineStr">
@@ -5959,21 +5965,17 @@
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>Óleos e Graxas Totais</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr"/>
       <c r="K54" s="4" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="L54" s="3" t="inlineStr">
-        <is>
-          <t>mg Óleos e Graxas/L</t>
-        </is>
-      </c>
+        <v>5.37</v>
+      </c>
+      <c r="L54" s="3" t="inlineStr"/>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>29,50 mg Óleos e Graxas/L</t>
+          <t>5,37 NA</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -5983,34 +5985,32 @@
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>entre 5,0 a 9,0</t>
         </is>
       </c>
       <c r="P54" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q54" s="5" t="n">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="Q54" s="5" t="n"/>
       <c r="R54" s="5" t="n">
-        <v>0.8</v>
+        <v>0.03</v>
       </c>
       <c r="S54" s="3" t="inlineStr">
         <is>
-          <t>SMWW 5520 D - 24ed.</t>
+          <t>SMWW 4500H+ B - 24ed.</t>
         </is>
       </c>
       <c r="T54" s="2" t="n">
-        <v>46301</v>
-      </c>
-      <c r="U54" s="9" t="inlineStr">
-        <is>
-          <t>Sem limite</t>
-        </is>
-      </c>
-      <c r="V54" s="9" t="inlineStr">
-        <is>
-          <t>Sem limite</t>
+        <v>46266</v>
+      </c>
+      <c r="U54" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="V54" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="W54" s="3" t="inlineStr">
@@ -6021,31 +6021,31 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46295.60416666666</v>
+        <v>46295.59722222222</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Represa 1</t>
+          <t>Lagoa 07</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Água bruta</t>
+          <t>Água residual</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Ribeirão Pamplona</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>4292-1/2026.0</t>
+          <t>4220-1/2026.0</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>4292/2026.0.A</t>
+          <t>4220/2026.0.A</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -6055,72 +6055,68 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>Físico-Químico</t>
+          <t>Efluentes</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>Alumínio Dissolvido</t>
-        </is>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
+          <t>Óleos e Graxas Totais</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr"/>
       <c r="K55" s="4" t="n">
-        <v>0.02</v>
+        <v>29.5</v>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>mg Al/L</t>
+          <t>mg Óleos e Graxas/L</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>&lt; 0,02 mg Al/L</t>
+          <t>29,50 mg Óleos e Graxas/L</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>CONAMA nº 357</t>
+          <t>Resolução Nº 430 - (Seção II)</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>até 0,1 mg/L</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P55" s="5" t="n">
-        <v>0.02</v>
+        <v>10</v>
       </c>
       <c r="Q55" s="5" t="n">
-        <v>0.01</v>
+        <v>3</v>
       </c>
       <c r="R55" s="5" t="n">
-        <v>0.01</v>
+        <v>0.8</v>
       </c>
       <c r="S55" s="3" t="inlineStr">
         <is>
-          <t>SMWW 3500-Al B - 24ed.</t>
+          <t>SMWW 5520 D - 24ed.</t>
         </is>
       </c>
       <c r="T55" s="2" t="n">
-        <v>46308.41666666666</v>
-      </c>
-      <c r="U55" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
-        </is>
-      </c>
-      <c r="V55" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
+        <v>46301</v>
+      </c>
+      <c r="U55" s="7" t="inlineStr">
+        <is>
+          <t>Sem limite</t>
+        </is>
+      </c>
+      <c r="V55" s="7" t="inlineStr">
+        <is>
+          <t>Sem limite</t>
         </is>
       </c>
       <c r="W55" s="3" t="inlineStr">
         <is>
-          <t>23c7c730a9a640c1846790f4e1b5f7e0</t>
+          <t>0634173a6d474a8c80b9a2b1502c7510</t>
         </is>
       </c>
     </row>
@@ -6165,7 +6161,7 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>Cloro residual</t>
+          <t>Alumínio Dissolvido</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -6174,16 +6170,16 @@
         </is>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>mg Cl/L</t>
+          <t>mg Al/L</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>&lt; 0,1 mg Cl/L</t>
+          <t>&lt; 0,02 mg Al/L</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
@@ -6193,34 +6189,34 @@
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>até 0,01 mg Cl/L</t>
+          <t>até 0,1 mg/L</t>
         </is>
       </c>
       <c r="P56" s="5" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="Q56" s="5" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="R56" s="5" t="n">
         <v>0.01</v>
       </c>
       <c r="S56" s="3" t="inlineStr">
         <is>
-          <t>SMWW 4500Cl G - 24ed.</t>
+          <t>SMWW 3500-Al B - 24ed.</t>
         </is>
       </c>
       <c r="T56" s="2" t="n">
-        <v>46298.35416666666</v>
+        <v>46308.41666666666</v>
       </c>
       <c r="U56" s="6" t="inlineStr">
         <is>
           <t>Conforme</t>
         </is>
       </c>
-      <c r="V56" s="7" t="inlineStr">
-        <is>
-          <t>Indeterminado</t>
+      <c r="V56" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="W56" s="3" t="inlineStr">
@@ -6245,17 +6241,17 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Montante e Jusante</t>
+          <t>Ribeirão Pamplona</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>4218-1/2026.0</t>
+          <t>4292-1/2026.0</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>4218/2026.0.A</t>
+          <t>4292/2026.0.A</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -6265,26 +6261,30 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>Microbiológico</t>
+          <t>Físico-Químico</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Coliformes termotolerantes</t>
-        </is>
-      </c>
-      <c r="J57" s="3" t="inlineStr"/>
+          <t>Cloro residual</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
       <c r="K57" s="4" t="n">
-        <v>270</v>
+        <v>0.1</v>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>NMP/100 mL</t>
+          <t>mg Cl/L</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>2,7x10² NMP/100 mL</t>
+          <t>&lt; 0,1 mg Cl/L</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
@@ -6294,39 +6294,39 @@
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>até 1.000NMP/100mL</t>
+          <t>até 0,01 mg Cl/L</t>
         </is>
       </c>
       <c r="P57" s="5" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="Q57" s="5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="R57" s="5" t="n">
-        <v>0.4</v>
+        <v>0.01</v>
       </c>
       <c r="S57" s="3" t="inlineStr">
         <is>
-          <t>SMWW 9221B, C e E - 24ed.</t>
+          <t>SMWW 4500Cl G - 24ed.</t>
         </is>
       </c>
       <c r="T57" s="2" t="n">
-        <v>46296.66666666666</v>
+        <v>46298.35416666666</v>
       </c>
       <c r="U57" s="6" t="inlineStr">
         <is>
           <t>Conforme</t>
         </is>
       </c>
-      <c r="V57" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
+          <t>Indeterminado</t>
         </is>
       </c>
       <c r="W57" s="3" t="inlineStr">
         <is>
-          <t>ffb347d20e274b5ea60d32c1e38b2081</t>
+          <t>23c7c730a9a640c1846790f4e1b5f7e0</t>
         </is>
       </c>
     </row>
@@ -6366,30 +6366,26 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Físico-Químico</t>
+          <t>Microbiológico</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>Cor Verdadeira</t>
-        </is>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
+          <t>Coliformes termotolerantes</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr"/>
       <c r="K58" s="4" t="n">
-        <v>0.6</v>
+        <v>270</v>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>mg Pt-Co/L</t>
+          <t>NMP/100 mL</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>&lt; 0,60 mg Pt-Co/L</t>
+          <t>2,7x10² NMP/100 mL</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
@@ -6399,25 +6395,25 @@
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>até 75 mg Pt-Co/L</t>
+          <t>até 1.000NMP/100mL</t>
         </is>
       </c>
       <c r="P58" s="5" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="Q58" s="5" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="R58" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="S58" s="3" t="inlineStr">
         <is>
-          <t>SMWW 2120C - 24ed.</t>
+          <t>SMWW 9221B, C e E - 24ed.</t>
         </is>
       </c>
       <c r="T58" s="2" t="n">
-        <v>46300.54166666666</v>
+        <v>46296.66666666666</v>
       </c>
       <c r="U58" s="6" t="inlineStr">
         <is>
@@ -6471,26 +6467,30 @@
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>Efluentes</t>
+          <t>Físico-Químico</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>DBO5</t>
-        </is>
-      </c>
-      <c r="J59" s="3" t="inlineStr"/>
+          <t>Cor Verdadeira</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
       <c r="K59" s="4" t="n">
-        <v>21.7</v>
+        <v>0.6</v>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>mg O2/L</t>
+          <t>mg Pt-Co/L</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>21,70 mgO2/L</t>
+          <t>&lt; 0,60 mg Pt-Co/L</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>até 5 mgO2/L</t>
+          <t>até 75 mg Pt-Co/L</t>
         </is>
       </c>
       <c r="P59" s="5" t="n">
@@ -6510,24 +6510,24 @@
         <v>0.6</v>
       </c>
       <c r="R59" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="S59" s="3" t="inlineStr">
         <is>
-          <t>SMWW 5210B - 24ed.</t>
+          <t>SMWW 2120C - 24ed.</t>
         </is>
       </c>
       <c r="T59" s="2" t="n">
-        <v>46296</v>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="V59" s="8" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
+        <v>46300.54166666666</v>
+      </c>
+      <c r="U59" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="V59" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="W59" s="3" t="inlineStr">
@@ -6572,17 +6572,17 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Físico-Químico</t>
+          <t>Efluentes</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>DQO</t>
+          <t>DBO5</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr"/>
       <c r="K60" s="4" t="n">
-        <v>46</v>
+        <v>21.7</v>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>46,00 mg O2/L</t>
+          <t>21,70 mgO2/L</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
@@ -6601,34 +6601,34 @@
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>até 5 mgO2/L</t>
         </is>
       </c>
       <c r="P60" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q60" s="5" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="R60" s="5" t="n">
-        <v>0.37</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S60" s="3" t="inlineStr">
         <is>
-          <t>MFQ 039.</t>
+          <t>SMWW 5210B - 24ed.</t>
         </is>
       </c>
       <c r="T60" s="2" t="n">
-        <v>46305.33333333334</v>
+        <v>46296</v>
       </c>
       <c r="U60" s="9" t="inlineStr">
         <is>
-          <t>Sem limite</t>
+          <t>Não conforme</t>
         </is>
       </c>
       <c r="V60" s="9" t="inlineStr">
         <is>
-          <t>Sem limite</t>
+          <t>Não conforme</t>
         </is>
       </c>
       <c r="W60" s="3" t="inlineStr">
@@ -6673,26 +6673,26 @@
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>Microbiológico</t>
+          <t>Físico-Químico</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <t>DQO</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr"/>
       <c r="K61" s="4" t="n">
-        <v>270</v>
+        <v>46</v>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>NMP/100 mL</t>
+          <t>mg O2/L</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>2,7x10² NMP/100 mL</t>
+          <t>46,00 mg O2/L</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -6706,28 +6706,28 @@
         </is>
       </c>
       <c r="P61" s="5" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="Q61" s="5" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="R61" s="5" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="S61" s="3" t="inlineStr">
         <is>
-          <t>SMWW 9221B, C e F - 24ed.</t>
+          <t>MFQ 039.</t>
         </is>
       </c>
       <c r="T61" s="2" t="n">
-        <v>46296.66666666666</v>
-      </c>
-      <c r="U61" s="9" t="inlineStr">
+        <v>46305.33333333334</v>
+      </c>
+      <c r="U61" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
       </c>
-      <c r="V61" s="9" t="inlineStr">
+      <c r="V61" s="7" t="inlineStr">
         <is>
           <t>Sem limite</t>
         </is>
@@ -6764,36 +6764,36 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>4218/2026.0</t>
+          <t>4218/2026.0.A</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Físico-Químico</t>
+          <t>Microbiológico</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>Fenóis</t>
+          <t>Escherichia coli</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr"/>
       <c r="K62" s="4" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>mg Fenol/L</t>
+          <t>NMP/100 mL</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>0,00 mg Fenol/L</t>
+          <t>2,7x10² NMP/100 mL</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
@@ -6803,34 +6803,34 @@
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>até 0,003 mg Fenol/L</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P62" s="5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q62" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R62" s="5" t="n">
-        <v>0.01</v>
+        <v>0.4</v>
       </c>
       <c r="S62" s="3" t="inlineStr">
         <is>
-          <t>SMWW 5530 C - 24ed.</t>
+          <t>SMWW 9221B, C e F - 24ed.</t>
         </is>
       </c>
       <c r="T62" s="2" t="n">
-        <v>46308.35416666666</v>
-      </c>
-      <c r="U62" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
-        </is>
-      </c>
-      <c r="V62" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
+        <v>46296.66666666666</v>
+      </c>
+      <c r="U62" s="7" t="inlineStr">
+        <is>
+          <t>Sem limite</t>
+        </is>
+      </c>
+      <c r="V62" s="7" t="inlineStr">
+        <is>
+          <t>Sem limite</t>
         </is>
       </c>
       <c r="W62" s="3" t="inlineStr">
@@ -6855,17 +6855,17 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Ribeirão Pamplona</t>
+          <t>Montante e Jusante</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>4292-1/2026.0</t>
+          <t>4218-1/2026.0</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>4292/2026.0</t>
+          <t>4218/2026.0</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -6880,15 +6880,21 @@
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>Materiais flutuantes</t>
+          <t>Fenóis</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr"/>
-      <c r="K63" s="4" t="n"/>
-      <c r="L63" s="3" t="inlineStr"/>
+      <c r="K63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>mg Fenol/L</t>
+        </is>
+      </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>Virtualmente Ausente</t>
+          <t>0,00 mg Fenol/L</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
@@ -6898,33 +6904,39 @@
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P63" s="5" t="n"/>
-      <c r="Q63" s="5" t="n"/>
-      <c r="R63" s="5" t="n"/>
+          <t>até 0,003 mg Fenol/L</t>
+        </is>
+      </c>
+      <c r="P63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" s="5" t="n">
+        <v>0.01</v>
+      </c>
       <c r="S63" s="3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>SMWW 5530 C - 24ed.</t>
         </is>
       </c>
       <c r="T63" s="2" t="n">
-        <v>46300.54166666666</v>
-      </c>
-      <c r="U63" s="9" t="inlineStr">
-        <is>
-          <t>Sem limite</t>
-        </is>
-      </c>
-      <c r="V63" s="9" t="inlineStr">
-        <is>
-          <t>Sem limite</t>
+        <v>46308.35416666666</v>
+      </c>
+      <c r="U63" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="V63" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
         </is>
       </c>
       <c r="W63" s="3" t="inlineStr">
         <is>
-          <t>23c7c730a9a640c1846790f4e1b5f7e0</t>
+          <t>ffb347d20e274b5ea60d32c1e38b2081</t>
         </is>
       </c>
     </row>
@@ -6944,50 +6956,40 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Montante e Jusante</t>
+          <t>Ribeirão Pamplona</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>4218-1/2026.0</t>
+          <t>4292-1/2026.0</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>4218/2026.0.A</t>
+          <t>4292/2026.0</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Efluentes</t>
+          <t>Físico-Químico</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>Oxigênio Dissolvido</t>
-        </is>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>&lt;</t>
-        </is>
-      </c>
-      <c r="K64" s="4" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L64" s="3" t="inlineStr">
-        <is>
-          <t>mg O2/L</t>
-        </is>
-      </c>
+          <t>Materiais flutuantes</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr"/>
+      <c r="K64" s="4" t="n"/>
+      <c r="L64" s="3" t="inlineStr"/>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>&lt; 0,02 mg O2/L</t>
+          <t>Virtualmente Ausente</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
@@ -6997,39 +6999,33 @@
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>não inferior a 5,0mg/L O2 mg O2/L</t>
-        </is>
-      </c>
-      <c r="P64" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="Q64" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="R64" s="5" t="n">
-        <v>0.02</v>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P64" s="5" t="n"/>
+      <c r="Q64" s="5" t="n"/>
+      <c r="R64" s="5" t="n"/>
       <c r="S64" s="3" t="inlineStr">
         <is>
-          <t>SMWW 4500O C - 24ed.</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="T64" s="2" t="n">
-        <v>46296</v>
-      </c>
-      <c r="U64" s="8" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="V64" s="8" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
+        <v>46300.54166666666</v>
+      </c>
+      <c r="U64" s="7" t="inlineStr">
+        <is>
+          <t>Sem limite</t>
+        </is>
+      </c>
+      <c r="V64" s="7" t="inlineStr">
+        <is>
+          <t>Sem limite</t>
         </is>
       </c>
       <c r="W64" s="3" t="inlineStr">
         <is>
-          <t>ffb347d20e274b5ea60d32c1e38b2081</t>
+          <t>23c7c730a9a640c1846790f4e1b5f7e0</t>
         </is>
       </c>
     </row>
@@ -7049,17 +7045,17 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Ribeirão Pamplona</t>
+          <t>Montante e Jusante</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>4292-1/2026.0</t>
+          <t>4218-1/2026.0</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>4292/2026.0.A</t>
+          <t>4218/2026.0.A</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -7077,9 +7073,13 @@
           <t>Oxigênio Dissolvido</t>
         </is>
       </c>
-      <c r="J65" s="3" t="inlineStr"/>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
       <c r="K65" s="4" t="n">
-        <v>7</v>
+        <v>0.02</v>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>7,00 mg O2/L</t>
+          <t>&lt; 0,02 mg O2/L</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
@@ -7116,21 +7116,21 @@
         </is>
       </c>
       <c r="T65" s="2" t="n">
-        <v>46297</v>
-      </c>
-      <c r="U65" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
-        </is>
-      </c>
-      <c r="V65" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
+        <v>46296</v>
+      </c>
+      <c r="U65" s="9" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="V65" s="9" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
         </is>
       </c>
       <c r="W65" s="3" t="inlineStr">
         <is>
-          <t>23c7c730a9a640c1846790f4e1b5f7e0</t>
+          <t>ffb347d20e274b5ea60d32c1e38b2081</t>
         </is>
       </c>
     </row>
@@ -7150,17 +7150,17 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Montante e Jusante</t>
+          <t>Ribeirão Pamplona</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>4218-1/2026.0</t>
+          <t>4292-1/2026.0</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>4218/2026.0.A</t>
+          <t>4292/2026.0.A</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -7170,26 +7170,26 @@
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>Físico-Químico</t>
+          <t>Efluentes</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>Turbidez</t>
+          <t>Oxigênio Dissolvido</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr"/>
       <c r="K66" s="4" t="n">
-        <v>0.84</v>
+        <v>7</v>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>NTU</t>
+          <t>mg O2/L</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>0,84 NTU</t>
+          <t>7,00 mg O2/L</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
@@ -7199,21 +7199,21 @@
       </c>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>até 100 NTU</t>
+          <t>não inferior a 5,0mg/L O2 mg O2/L</t>
         </is>
       </c>
       <c r="P66" s="5" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="Q66" s="5" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="R66" s="5" t="n">
-        <v>0.25</v>
+        <v>0.02</v>
       </c>
       <c r="S66" s="3" t="inlineStr">
         <is>
-          <t>SMWW 2130B - 24ed.</t>
+          <t>SMWW 4500O C - 24ed.</t>
         </is>
       </c>
       <c r="T66" s="2" t="n">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="W66" s="3" t="inlineStr">
         <is>
-          <t>ffb347d20e274b5ea60d32c1e38b2081</t>
+          <t>23c7c730a9a640c1846790f4e1b5f7e0</t>
         </is>
       </c>
     </row>
@@ -7276,17 +7276,21 @@
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>Turbidez</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr"/>
       <c r="K67" s="4" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="L67" s="3" t="inlineStr"/>
+        <v>0.84</v>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>NTU</t>
+        </is>
+      </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>6,85 NA</t>
+          <t>0,84 NTU</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
@@ -7296,23 +7300,25 @@
       </c>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>Entre 6 e 9. NA</t>
+          <t>até 100 NTU</t>
         </is>
       </c>
       <c r="P67" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q67" s="5" t="n"/>
+        <v>0.5</v>
+      </c>
+      <c r="Q67" s="5" t="n">
+        <v>0.1</v>
+      </c>
       <c r="R67" s="5" t="n">
-        <v>0.03</v>
+        <v>0.25</v>
       </c>
       <c r="S67" s="3" t="inlineStr">
         <is>
-          <t>SMWW 4500H+ B - 24ed.</t>
+          <t>SMWW 2130B - 24ed.</t>
         </is>
       </c>
       <c r="T67" s="2" t="n">
-        <v>46296.66666666666</v>
+        <v>46297</v>
       </c>
       <c r="U67" s="6" t="inlineStr">
         <is>
@@ -7371,72 +7377,167 @@
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr"/>
+      <c r="K68" s="4" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="L68" s="3" t="inlineStr"/>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>6,85 NA</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
+          <t>CONAMA nº 357</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>Entre 6 e 9. NA</t>
+        </is>
+      </c>
+      <c r="P68" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q68" s="5" t="n"/>
+      <c r="R68" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S68" s="3" t="inlineStr">
+        <is>
+          <t>SMWW 4500H+ B - 24ed.</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="n">
+        <v>46296.66666666666</v>
+      </c>
+      <c r="U68" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="V68" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="W68" s="3" t="inlineStr">
+        <is>
+          <t>ffb347d20e274b5ea60d32c1e38b2081</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46295.60416666666</v>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Represa 1</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Água bruta</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Montante e Jusante</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>4218-1/2026.0</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>4218/2026.0.A</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>Físico-Químico</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
           <t>Óleos e Graxas Totais</t>
         </is>
       </c>
-      <c r="J68" s="3" t="inlineStr">
+      <c r="J69" s="3" t="inlineStr">
         <is>
           <t>&lt;</t>
         </is>
       </c>
-      <c r="K68" s="4" t="n">
+      <c r="K69" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="L68" s="3" t="inlineStr">
+      <c r="L69" s="3" t="inlineStr">
         <is>
           <t>mg Óleos e Graxas/L</t>
         </is>
       </c>
-      <c r="M68" s="3" t="inlineStr">
+      <c r="M69" s="3" t="inlineStr">
         <is>
           <t>&lt; 10,00 mg Óleos e Graxas/L</t>
         </is>
       </c>
-      <c r="N68" s="3" t="inlineStr">
+      <c r="N69" s="3" t="inlineStr">
         <is>
           <t>CONAMA nº 357</t>
         </is>
       </c>
-      <c r="O68" s="3" t="inlineStr">
+      <c r="O69" s="3" t="inlineStr">
         <is>
           <t>Virtualmente ausente</t>
         </is>
       </c>
-      <c r="P68" s="5" t="n">
+      <c r="P69" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="Q68" s="5" t="n">
+      <c r="Q69" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="R68" s="5" t="n">
+      <c r="R69" s="5" t="n">
         <v>0.8</v>
       </c>
-      <c r="S68" s="3" t="inlineStr">
+      <c r="S69" s="3" t="inlineStr">
         <is>
           <t>SMWW 5520 D - 24ed.</t>
         </is>
       </c>
-      <c r="T68" s="2" t="n">
+      <c r="T69" s="2" t="n">
         <v>46308.41666666666</v>
       </c>
-      <c r="U68" s="6" t="inlineStr">
+      <c r="U69" s="6" t="inlineStr">
         <is>
           <t>Conforme</t>
         </is>
       </c>
-      <c r="V68" s="9" t="inlineStr">
+      <c r="V69" s="7" t="inlineStr">
         <is>
           <t>Não verificável</t>
         </is>
       </c>
-      <c r="W68" s="3" t="inlineStr">
+      <c r="W69" s="3" t="inlineStr">
         <is>
           <t>ffb347d20e274b5ea60d32c1e38b2081</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W68"/>
+  <autoFilter ref="A1:W69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7447,11 +7548,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y11"/>
+  <dimension ref="A1:Y12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -7472,7 +7573,7 @@
     <col width="20" customWidth="1" min="20" max="20"/>
     <col width="20" customWidth="1" min="21" max="21"/>
     <col width="17" customWidth="1" min="22" max="22"/>
-    <col width="23" customWidth="1" min="23" max="23"/>
+    <col width="49" customWidth="1" min="23" max="23"/>
     <col width="55" customWidth="1" min="24" max="24"/>
     <col width="34" customWidth="1" min="25" max="25"/>
   </cols>
@@ -7606,35 +7707,35 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46295.47916666666</v>
+        <v>46259.56944444445</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Goiabal</t>
+          <t>Bomba De Captação De Efluentes - Efluente Bruto</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Água bruta</t>
+          <t>Água residual</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Goiabal</t>
+          <t>Conama 430</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>4293-1/2026.0</t>
+          <t>1081-1/2026.0</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>4293/2026.0.A</t>
+          <t>1081/2026.0.A + 1081/2026.0</t>
         </is>
       </c>
       <c r="G2" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
@@ -7643,10 +7744,10 @@
       </c>
       <c r="I2" s="3" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>46296.60416666666</v>
+        <v>46262.45555555556</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>46315.42569444444</v>
+        <v>46282.66180555556</v>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
@@ -7681,47 +7782,47 @@
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>PC 389/26</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>PC811/2026</t>
+          <t>PC389/2026</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>CA961/2026</t>
+          <t>CA434/2026</t>
         </is>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>Daniel D'Ángelo</t>
+          <t>Danilo .</t>
         </is>
       </c>
       <c r="W2" s="3" t="inlineStr">
         <is>
-          <t>GOIABAL</t>
+          <t>BOMBA DE CAPTAÇÃO DE EFLUENTES - EFLUENTE BRUTO</t>
         </is>
       </c>
       <c r="X2" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_GOIABAL_4293-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-08\2026-08-25_AR_BOMBA-DE-CAPTACAO-DE-EFLUENTES-EFLUENTE-BRUTO_1081-2026.pdf</t>
         </is>
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
-          <t>d552c76bd7854cefae97a690cf7f9dd4</t>
+          <t>f6136d7c8d5043028ae926545fdfde9d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46295.48611111111</v>
+        <v>46295.47916666666</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Montante</t>
+          <t>Goiabal</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -7731,21 +7832,21 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Montante</t>
+          <t>Goiabal</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>4296-1/2026.0</t>
+          <t>4293-1/2026.0</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>4296/2026.0.A</t>
+          <t>4293/2026.0.A</t>
         </is>
       </c>
       <c r="G3" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
@@ -7757,7 +7858,7 @@
         <v>46296.60416666666</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>46315.42916666667</v>
+        <v>46315.42569444444</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -7812,27 +7913,27 @@
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>MONTANTE</t>
+          <t>GOIABAL</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_MONTANTE_4296-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_GOIABAL_4293-2026.pdf</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>26c03a970cb54efab5ba85cb5e1ef425</t>
+          <t>d552c76bd7854cefae97a690cf7f9dd4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46295.48958333334</v>
+        <v>46295.48611111111</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Jusante</t>
+          <t>Montante</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -7842,21 +7943,21 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Jusante</t>
+          <t>Montante</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>4294-1/2026.0</t>
+          <t>4296-1/2026.0</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>4294/2026.0.A + 4294/2026.0</t>
+          <t>4296/2026.0.A</t>
         </is>
       </c>
       <c r="G4" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
@@ -7868,7 +7969,7 @@
         <v>46296.60416666666</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>46315.42638888889</v>
+        <v>46315.42916666667</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
@@ -7878,7 +7979,7 @@
       <c r="M4" s="3" t="n"/>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -7923,27 +8024,27 @@
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>JUSANTE</t>
+          <t>MONTANTE</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_JUSANTE_4294-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_MONTANTE_4296-2026.pdf</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>1563178792344916a8607c4c610e5849</t>
+          <t>26c03a970cb54efab5ba85cb5e1ef425</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46295.5</v>
+        <v>46295.48958333334</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Captação</t>
+          <t>Jusante</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -7953,21 +8054,21 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Captação</t>
+          <t>Jusante</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>4295-1/2026.0</t>
+          <t>4294-1/2026.0</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>4295/2026.0.A</t>
+          <t>4294/2026.0.A + 4294/2026.0</t>
         </is>
       </c>
       <c r="G5" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
@@ -7979,7 +8080,7 @@
         <v>46296.60416666666</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>46315.42916666667</v>
+        <v>46315.42638888889</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -8034,27 +8135,27 @@
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>CAPTAÇÃO</t>
+          <t>JUSANTE</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_CAPTACAO_4295-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_JUSANTE_4294-2026.pdf</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>646404d0f8884d71b4e2c86ee93ee05c</t>
+          <t>1563178792344916a8607c4c610e5849</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46295.50902777778</v>
+        <v>46295.5</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Saída da Mina</t>
+          <t>Captação</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -8064,37 +8165,33 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Saída Mina</t>
+          <t>Captação</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>4291-1/2026.0</t>
+          <t>4295-1/2026.0</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>4291/2026.0.A + 4291/2026.0</t>
+          <t>4295/2026.0.A</t>
         </is>
       </c>
       <c r="G6" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>Ferro dissolvido</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="2" t="n">
         <v>46296.60416666666</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>46315.42222222222</v>
+        <v>46315.42916666667</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
@@ -8104,7 +8201,7 @@
       <c r="M6" s="3" t="n"/>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -8149,27 +8246,27 @@
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>SAIDA DA MINA</t>
+          <t>CAPTAÇÃO</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_SAIDA-DA-MINA_4291-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_CAPTACAO_4295-2026.pdf</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>c404d556c3a34a0382e0ecb403b34ae8</t>
+          <t>646404d0f8884d71b4e2c86ee93ee05c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46295.51388888889</v>
+        <v>46295.50902777778</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Jusante</t>
+          <t>Saída da Mina</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -8179,159 +8276,163 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Montante e Jusante</t>
+          <t>Saída Mina</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>4219-1/2026.0</t>
+          <t>4291-1/2026.0</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>4219/2026.0.A + 4219/2026.0</t>
+          <t>4291/2026.0.A + 4291/2026.0</t>
         </is>
       </c>
       <c r="G7" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>Não conforme</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Coliformes termotolerantes, Demanda bioquímica de oxigênio (DBO5 dias a 20°C), Fenóis, Oxigênio Dissolvido</t>
+          <t>Ferro dissolvido</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>46296.54166666666</v>
+        <v>46296.60416666666</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>46315.41527777778</v>
+        <v>46315.42222222222</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>CONFORME</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>Contratante</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>CONFORME</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t>Contratante</t>
-        </is>
-      </c>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>PC389/2026</t>
+          <t>PC811/2026</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>CA960/2026</t>
+          <t>CA961/2026</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>Danilo .</t>
+          <t>Daniel D'Ángelo</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>JUSANTE</t>
+          <t>SAIDA DA MINA</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_JUSANTE_4219-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_SAIDA-DA-MINA_4291-2026.pdf</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>ddaf07d7cbcf4dbc81240b851f9b3df3</t>
+          <t>c404d556c3a34a0382e0ecb403b34ae8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46295.59027777778</v>
+        <v>46295.51388888889</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Lagoa 01</t>
+          <t>Jusante</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Água residual</t>
+          <t>Água bruta</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Montante e Jusante</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>4221-1/2026.0</t>
+          <t>4219-1/2026.0</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>4221/2026.0.A + 4221/2026.0</t>
+          <t>4219/2026.0.A + 4219/2026.0</t>
         </is>
       </c>
       <c r="G8" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Conforme</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Coliformes termotolerantes, Demanda bioquímica de oxigênio (DBO5 dias a 20°C), Fenóis, Oxigênio Dissolvido</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="n">
         <v>46296.54166666666</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>46315.41875</v>
+        <v>46315.41527777778</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="M8" s="3" t="n"/>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -8379,27 +8480,27 @@
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>LAGOA 01</t>
+          <t>JUSANTE</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AR_LAGOA-01_4221-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_JUSANTE_4219-2026.pdf</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>866cb8e68ec148f2a374c988ec5f44ed</t>
+          <t>ddaf07d7cbcf4dbc81240b851f9b3df3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46295.59722222222</v>
+        <v>46295.59027777778</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Lagoa 07</t>
+          <t>Lagoa 01</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -8414,12 +8515,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>4220-1/2026.0</t>
+          <t>4221-1/2026.0</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>4220/2026.0.A + 4220/2026.0</t>
+          <t>4221/2026.0.A + 4221/2026.0</t>
         </is>
       </c>
       <c r="G9" s="10" t="n">
@@ -8432,10 +8533,10 @@
       </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="2" t="n">
-        <v>46296.59722222222</v>
+        <v>46296.54166666666</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>46315.41736111111</v>
+        <v>46315.41875</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -8490,108 +8591,100 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>LAGOA 7</t>
+          <t>LAGOA 01</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AR_LAGOA-07_4220-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AR_LAGOA-01_4221-2026.pdf</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>0634173a6d474a8c80b9a2b1502c7510</t>
+          <t>866cb8e68ec148f2a374c988ec5f44ed</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46295.60416666666</v>
+        <v>46295.59722222222</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Represa 1</t>
+          <t>Lagoa 07</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Água bruta</t>
+          <t>Água residual</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Montante e Jusante</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>4218-1/2026.0</t>
+          <t>4220-1/2026.0</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>4218/2026.0.A + 4218/2026.0</t>
+          <t>4220/2026.0.A + 4220/2026.0</t>
         </is>
       </c>
       <c r="G10" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>Não conforme</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>Demanda bioquímica de oxigênio (DBO5 dias a 20°C), Oxigênio Dissolvido</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="2" t="n">
-        <v>46296.54166666666</v>
+        <v>46296.59722222222</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>46315.40555555555</v>
+        <v>46315.41736111111</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="M10" s="3" t="n"/>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>CONFORME</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>Contratante</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t>CONFORME</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="inlineStr">
-        <is>
-          <t>Contratante</t>
-        </is>
-      </c>
-      <c r="S10" s="3" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
           <t>PC389/2026</t>
@@ -8609,17 +8702,17 @@
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>REPRESA 1</t>
+          <t>LAGOA 7</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_REPRESA-1_4218-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AR_LAGOA-07_4220-2026.pdf</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>ffb347d20e274b5ea60d32c1e38b2081</t>
+          <t>0634173a6d474a8c80b9a2b1502c7510</t>
         </is>
       </c>
     </row>
@@ -8639,103 +8732,222 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
+          <t>Montante e Jusante</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>4218-1/2026.0</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>4218/2026.0.A + 4218/2026.0</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>Não conforme</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Demanda bioquímica de oxigênio (DBO5 dias a 20°C), Oxigênio Dissolvido</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>46296.54166666666</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>46315.40555555555</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>CONFORME</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>Contratante</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>PC389/2026</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>CA960/2026</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>Danilo .</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>REPRESA 1</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_REPRESA-1_4218-2026.pdf</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>ffb347d20e274b5ea60d32c1e38b2081</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46295.60416666666</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Represa 1</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Água bruta</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
           <t>Ribeirão Pamplona</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>4292-1/2026.0</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>4292/2026.0.A + 4292/2026.0</t>
         </is>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="G12" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Conforme</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="2" t="n">
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="2" t="n">
         <v>46296.60416666666</v>
       </c>
-      <c r="K11" s="2" t="n">
+      <c r="K12" s="2" t="n">
         <v>46315.425</v>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="M12" s="3" t="n"/>
+      <c r="N12" s="3" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr">
+      <c r="P12" s="3" t="inlineStr">
         <is>
           <t>---</t>
         </is>
       </c>
-      <c r="Q11" s="3" t="inlineStr">
+      <c r="Q12" s="3" t="inlineStr">
         <is>
           <t>CONFORME</t>
         </is>
       </c>
-      <c r="R11" s="3" t="inlineStr">
+      <c r="R12" s="3" t="inlineStr">
         <is>
           <t>Contratante</t>
         </is>
       </c>
-      <c r="S11" s="3" t="inlineStr">
+      <c r="S12" s="3" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T11" s="3" t="inlineStr">
+      <c r="T12" s="3" t="inlineStr">
         <is>
           <t>PC811/2026</t>
         </is>
       </c>
-      <c r="U11" s="3" t="inlineStr">
+      <c r="U12" s="3" t="inlineStr">
         <is>
           <t>CA961/2026</t>
         </is>
       </c>
-      <c r="V11" s="3" t="inlineStr">
+      <c r="V12" s="3" t="inlineStr">
         <is>
           <t>Daniel D'Ángelo</t>
         </is>
       </c>
-      <c r="W11" s="3" t="inlineStr">
+      <c r="W12" s="3" t="inlineStr">
         <is>
           <t>REPRESA 1</t>
         </is>
       </c>
-      <c r="X11" s="3" t="inlineStr">
+      <c r="X12" s="3" t="inlineStr">
         <is>
           <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_REPRESA-1_4292-2026.pdf</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
+      <c r="Y12" s="3" t="inlineStr">
         <is>
           <t>23c7c730a9a640c1846790f4e1b5f7e0</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y11"/>
+  <autoFilter ref="A1:Y12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8746,7 +8958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y11"/>
+  <dimension ref="A1:Y12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8905,46 +9117,34 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="n">
-        <v>46295.47916666666</v>
+        <v>46259.56944444445</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Goiabal</t>
+          <t>Bomba De Captação De Efluentes - Efluente Bruto</t>
         </is>
       </c>
       <c r="C2" s="12" t="n"/>
-      <c r="D2" s="13" t="inlineStr">
-        <is>
-          <t>&lt; 0,02 mg Al/L</t>
-        </is>
-      </c>
+      <c r="D2" s="12" t="n"/>
       <c r="E2" s="12" t="n"/>
-      <c r="F2" s="13" t="inlineStr">
-        <is>
-          <t>&lt; 0,1 mg Cl/L</t>
-        </is>
-      </c>
+      <c r="F2" s="12" t="n"/>
       <c r="G2" s="12" t="n"/>
       <c r="H2" s="12" t="n"/>
       <c r="I2" s="12" t="n"/>
       <c r="J2" s="12" t="n"/>
-      <c r="K2" s="12" t="n"/>
+      <c r="K2" s="13" t="inlineStr">
+        <is>
+          <t>879,00 mgO2/L</t>
+        </is>
+      </c>
       <c r="L2" s="12" t="n"/>
       <c r="M2" s="12" t="n"/>
       <c r="N2" s="12" t="n"/>
-      <c r="O2" s="13" t="inlineStr">
-        <is>
-          <t>0,06 mg Fe/L</t>
-        </is>
-      </c>
+      <c r="O2" s="12" t="n"/>
       <c r="P2" s="12" t="n"/>
       <c r="Q2" s="12" t="n"/>
       <c r="R2" s="12" t="n"/>
-      <c r="S2" s="13" t="inlineStr">
-        <is>
-          <t>7,20 mg O2/L</t>
-        </is>
-      </c>
+      <c r="S2" s="12" t="n"/>
       <c r="T2" s="12" t="n"/>
       <c r="U2" s="12" t="n"/>
       <c r="V2" s="12" t="n"/>
@@ -8954,17 +9154,25 @@
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>46295.48611111111</v>
+        <v>46295.47916666666</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Montante</t>
+          <t>Goiabal</t>
         </is>
       </c>
       <c r="C3" s="12" t="n"/>
-      <c r="D3" s="12" t="n"/>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>&lt; 0,02 mg Al/L</t>
+        </is>
+      </c>
       <c r="E3" s="12" t="n"/>
-      <c r="F3" s="12" t="n"/>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>&lt; 0,1 mg Cl/L</t>
+        </is>
+      </c>
       <c r="G3" s="12" t="n"/>
       <c r="H3" s="12" t="n"/>
       <c r="I3" s="12" t="n"/>
@@ -8973,13 +9181,17 @@
       <c r="L3" s="12" t="n"/>
       <c r="M3" s="12" t="n"/>
       <c r="N3" s="12" t="n"/>
-      <c r="O3" s="12" t="n"/>
+      <c r="O3" s="13" t="inlineStr">
+        <is>
+          <t>0,06 mg Fe/L</t>
+        </is>
+      </c>
       <c r="P3" s="12" t="n"/>
       <c r="Q3" s="12" t="n"/>
       <c r="R3" s="12" t="n"/>
       <c r="S3" s="13" t="inlineStr">
         <is>
-          <t>7,10 mg O2/L</t>
+          <t>7,20 mg O2/L</t>
         </is>
       </c>
       <c r="T3" s="12" t="n"/>
@@ -8991,30 +9203,18 @@
     </row>
     <row r="4">
       <c r="A4" s="11" t="n">
-        <v>46295.48958333334</v>
+        <v>46295.48611111111</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jusante</t>
+          <t>Montante</t>
         </is>
       </c>
       <c r="C4" s="12" t="n"/>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>&lt; 0,01 mg Al/L</t>
-        </is>
-      </c>
+      <c r="D4" s="12" t="n"/>
       <c r="E4" s="12" t="n"/>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>&lt; 0,1 mg Cl/L</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>0,008 mgCu/L</t>
-        </is>
-      </c>
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="12" t="n"/>
       <c r="H4" s="12" t="n"/>
       <c r="I4" s="12" t="n"/>
       <c r="J4" s="12" t="n"/>
@@ -9028,7 +9228,7 @@
       <c r="R4" s="12" t="n"/>
       <c r="S4" s="13" t="inlineStr">
         <is>
-          <t>7,00 mg O2/L</t>
+          <t>7,10 mg O2/L</t>
         </is>
       </c>
       <c r="T4" s="12" t="n"/>
@@ -9040,22 +9240,30 @@
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
-        <v>46295.5</v>
+        <v>46295.48958333334</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Captação</t>
+          <t>Jusante</t>
         </is>
       </c>
       <c r="C5" s="12" t="n"/>
-      <c r="D5" s="12" t="n"/>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>&lt; 0,01 mg Al/L</t>
+        </is>
+      </c>
       <c r="E5" s="12" t="n"/>
       <c r="F5" s="13" t="inlineStr">
         <is>
           <t>&lt; 0,1 mg Cl/L</t>
         </is>
       </c>
-      <c r="G5" s="12" t="n"/>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>0,008 mgCu/L</t>
+        </is>
+      </c>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
@@ -9069,7 +9277,7 @@
       <c r="R5" s="12" t="n"/>
       <c r="S5" s="13" t="inlineStr">
         <is>
-          <t>7,40 mg O2/L</t>
+          <t>7,00 mg O2/L</t>
         </is>
       </c>
       <c r="T5" s="12" t="n"/>
@@ -9081,26 +9289,22 @@
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
-        <v>46295.50902777778</v>
+        <v>46295.5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Saída da Mina</t>
+          <t>Captação</t>
         </is>
       </c>
       <c r="C6" s="12" t="n"/>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>0,05 mg Al/L</t>
-        </is>
-      </c>
+      <c r="D6" s="12" t="n"/>
       <c r="E6" s="12" t="n"/>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>0,009 mgCu/L</t>
-        </is>
-      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>&lt; 0,1 mg Cl/L</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="12" t="n"/>
@@ -9108,17 +9312,13 @@
       <c r="L6" s="12" t="n"/>
       <c r="M6" s="12" t="n"/>
       <c r="N6" s="12" t="n"/>
-      <c r="O6" s="14" t="inlineStr">
-        <is>
-          <t>3,20 mg Fe/L</t>
-        </is>
-      </c>
+      <c r="O6" s="12" t="n"/>
       <c r="P6" s="12" t="n"/>
       <c r="Q6" s="12" t="n"/>
       <c r="R6" s="12" t="n"/>
       <c r="S6" s="13" t="inlineStr">
         <is>
-          <t>7,10 mg O2/L</t>
+          <t>7,40 mg O2/L</t>
         </is>
       </c>
       <c r="T6" s="12" t="n"/>
@@ -9130,178 +9330,138 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>46295.51388888889</v>
+        <v>46295.50902777778</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jusante</t>
+          <t>Saída da Mina</t>
         </is>
       </c>
       <c r="C7" s="12" t="n"/>
-      <c r="D7" s="12" t="n"/>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>0,05 mg Al/L</t>
+        </is>
+      </c>
       <c r="E7" s="12" t="n"/>
       <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t>9x10³ NMP/100 mL</t>
-        </is>
-      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>0,009 mgCu/L</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="13" t="inlineStr">
-        <is>
-          <t>&lt; 0,60 mg Pt-Co/L</t>
-        </is>
-      </c>
-      <c r="K7" s="14" t="inlineStr">
-        <is>
-          <t>69,00 mgO2/L</t>
-        </is>
-      </c>
-      <c r="L7" s="15" t="inlineStr">
-        <is>
-          <t>128,00 mg O2/L</t>
-        </is>
-      </c>
-      <c r="M7" s="15" t="inlineStr">
-        <is>
-          <t>9x10³ NMP/100 mL</t>
-        </is>
-      </c>
-      <c r="N7" s="14" t="inlineStr">
-        <is>
-          <t>0,04 mg Fenol/L</t>
-        </is>
-      </c>
-      <c r="O7" s="12" t="n"/>
+      <c r="J7" s="12" t="n"/>
+      <c r="K7" s="12" t="n"/>
+      <c r="L7" s="12" t="n"/>
+      <c r="M7" s="12" t="n"/>
+      <c r="N7" s="12" t="n"/>
+      <c r="O7" s="14" t="inlineStr">
+        <is>
+          <t>3,20 mg Fe/L</t>
+        </is>
+      </c>
       <c r="P7" s="12" t="n"/>
       <c r="Q7" s="12" t="n"/>
       <c r="R7" s="12" t="n"/>
-      <c r="S7" s="14" t="inlineStr">
-        <is>
-          <t>0,10 mg O2/L</t>
+      <c r="S7" s="13" t="inlineStr">
+        <is>
+          <t>7,10 mg O2/L</t>
         </is>
       </c>
       <c r="T7" s="12" t="n"/>
       <c r="U7" s="12" t="n"/>
       <c r="V7" s="12" t="n"/>
-      <c r="W7" s="13" t="inlineStr">
-        <is>
-          <t>3,78 NTU</t>
-        </is>
-      </c>
-      <c r="X7" s="13" t="inlineStr">
-        <is>
-          <t>6,82 NA</t>
-        </is>
-      </c>
-      <c r="Y7" s="13" t="inlineStr">
-        <is>
-          <t>&lt; 10,00 mg Óleos e Graxas/L</t>
-        </is>
-      </c>
+      <c r="W7" s="12" t="n"/>
+      <c r="X7" s="12" t="n"/>
+      <c r="Y7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
-        <v>46295.59027777778</v>
+        <v>46295.51388888889</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lagoa 01</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>56,00 mgCaCO3/L</t>
-        </is>
-      </c>
+          <t>Jusante</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="n"/>
       <c r="D8" s="12" t="n"/>
-      <c r="E8" s="15" t="inlineStr">
-        <is>
-          <t>6,81 NH3</t>
-        </is>
-      </c>
+      <c r="E8" s="12" t="n"/>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
-      <c r="H8" s="12" t="n"/>
-      <c r="I8" s="15" t="inlineStr">
-        <is>
-          <t>405,00 µS/cm</t>
-        </is>
-      </c>
-      <c r="J8" s="12" t="n"/>
-      <c r="K8" s="13" t="inlineStr">
-        <is>
-          <t>504,71 mgO2/L</t>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>9x10³ NMP/100 mL</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="n"/>
+      <c r="J8" s="13" t="inlineStr">
+        <is>
+          <t>&lt; 0,60 mg Pt-Co/L</t>
+        </is>
+      </c>
+      <c r="K8" s="14" t="inlineStr">
+        <is>
+          <t>69,00 mgO2/L</t>
         </is>
       </c>
       <c r="L8" s="15" t="inlineStr">
         <is>
-          <t>1394,00 mg O2/L</t>
-        </is>
-      </c>
-      <c r="M8" s="12" t="n"/>
-      <c r="N8" s="13" t="inlineStr">
-        <is>
-          <t>&lt; 0,00 mg Fenol/L</t>
+          <t>128,00 mg O2/L</t>
+        </is>
+      </c>
+      <c r="M8" s="15" t="inlineStr">
+        <is>
+          <t>9x10³ NMP/100 mL</t>
+        </is>
+      </c>
+      <c r="N8" s="14" t="inlineStr">
+        <is>
+          <t>0,04 mg Fenol/L</t>
         </is>
       </c>
       <c r="O8" s="12" t="n"/>
-      <c r="P8" s="15" t="inlineStr">
-        <is>
-          <t>11,06 mg P/L</t>
-        </is>
-      </c>
+      <c r="P8" s="12" t="n"/>
       <c r="Q8" s="12" t="n"/>
-      <c r="R8" s="15" t="inlineStr">
-        <is>
-          <t>14,00 mgNKT/L</t>
-        </is>
-      </c>
-      <c r="S8" s="15" t="inlineStr">
-        <is>
-          <t>&lt; 0,02 mg O2/L</t>
-        </is>
-      </c>
-      <c r="T8" s="15" t="inlineStr">
-        <is>
-          <t>103,0000 mg/L</t>
-        </is>
-      </c>
-      <c r="U8" s="15" t="inlineStr">
-        <is>
-          <t>50,00 mg/L</t>
-        </is>
-      </c>
-      <c r="V8" s="15" t="inlineStr">
-        <is>
-          <t>38,00 mg/L</t>
-        </is>
-      </c>
-      <c r="W8" s="12" t="n"/>
+      <c r="R8" s="12" t="n"/>
+      <c r="S8" s="14" t="inlineStr">
+        <is>
+          <t>0,10 mg O2/L</t>
+        </is>
+      </c>
+      <c r="T8" s="12" t="n"/>
+      <c r="U8" s="12" t="n"/>
+      <c r="V8" s="12" t="n"/>
+      <c r="W8" s="13" t="inlineStr">
+        <is>
+          <t>3,78 NTU</t>
+        </is>
+      </c>
       <c r="X8" s="13" t="inlineStr">
         <is>
-          <t>5,26 NA</t>
-        </is>
-      </c>
-      <c r="Y8" s="15" t="inlineStr">
-        <is>
-          <t>19,50 mg Óleos e Graxas/L</t>
+          <t>6,82 NA</t>
+        </is>
+      </c>
+      <c r="Y8" s="13" t="inlineStr">
+        <is>
+          <t>&lt; 10,00 mg Óleos e Graxas/L</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46295.59722222222</v>
+        <v>46295.59027777778</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lagoa 07</t>
+          <t>Lagoa 01</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>88,00 mgCaCO3/L</t>
+          <t>56,00 mgCaCO3/L</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
@@ -9315,30 +9475,30 @@
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="15" t="inlineStr">
         <is>
-          <t>457,00 µS/cm</t>
+          <t>405,00 µS/cm</t>
         </is>
       </c>
       <c r="J9" s="12" t="n"/>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>382,50 mgO2/L</t>
+          <t>504,71 mgO2/L</t>
         </is>
       </c>
       <c r="L9" s="15" t="inlineStr">
         <is>
-          <t>1060,00 mg O2/L</t>
+          <t>1394,00 mg O2/L</t>
         </is>
       </c>
       <c r="M9" s="12" t="n"/>
       <c r="N9" s="13" t="inlineStr">
         <is>
-          <t>0,14 mg Fenol/L</t>
+          <t>&lt; 0,00 mg Fenol/L</t>
         </is>
       </c>
       <c r="O9" s="12" t="n"/>
       <c r="P9" s="15" t="inlineStr">
         <is>
-          <t>7,25 mg P/L</t>
+          <t>11,06 mg P/L</t>
         </is>
       </c>
       <c r="Q9" s="12" t="n"/>
@@ -9354,101 +9514,117 @@
       </c>
       <c r="T9" s="15" t="inlineStr">
         <is>
-          <t>215,0000 mg/L</t>
+          <t>103,0000 mg/L</t>
         </is>
       </c>
       <c r="U9" s="15" t="inlineStr">
         <is>
-          <t>138,00 mg/L</t>
+          <t>50,00 mg/L</t>
         </is>
       </c>
       <c r="V9" s="15" t="inlineStr">
         <is>
-          <t>102,00 mg/L</t>
+          <t>38,00 mg/L</t>
         </is>
       </c>
       <c r="W9" s="12" t="n"/>
       <c r="X9" s="13" t="inlineStr">
         <is>
-          <t>5,37 NA</t>
+          <t>5,26 NA</t>
         </is>
       </c>
       <c r="Y9" s="15" t="inlineStr">
         <is>
-          <t>29,50 mg Óleos e Graxas/L</t>
+          <t>19,50 mg Óleos e Graxas/L</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="n">
-        <v>46295.60416666666</v>
+        <v>46295.59722222222</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Represa 1</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="n"/>
+          <t>Lagoa 07</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>88,00 mgCaCO3/L</t>
+        </is>
+      </c>
       <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>6,81 NH3</t>
+        </is>
+      </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>2,7x10² NMP/100 mL</t>
-        </is>
-      </c>
-      <c r="I10" s="12" t="n"/>
-      <c r="J10" s="13" t="inlineStr">
-        <is>
-          <t>&lt; 0,60 mg Pt-Co/L</t>
-        </is>
-      </c>
-      <c r="K10" s="14" t="inlineStr">
-        <is>
-          <t>21,70 mgO2/L</t>
+      <c r="H10" s="12" t="n"/>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>457,00 µS/cm</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="n"/>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>382,50 mgO2/L</t>
         </is>
       </c>
       <c r="L10" s="15" t="inlineStr">
         <is>
-          <t>46,00 mg O2/L</t>
-        </is>
-      </c>
-      <c r="M10" s="15" t="inlineStr">
-        <is>
-          <t>2,7x10² NMP/100 mL</t>
-        </is>
-      </c>
+          <t>1060,00 mg O2/L</t>
+        </is>
+      </c>
+      <c r="M10" s="12" t="n"/>
       <c r="N10" s="13" t="inlineStr">
         <is>
-          <t>0,00 mg Fenol/L</t>
+          <t>0,14 mg Fenol/L</t>
         </is>
       </c>
       <c r="O10" s="12" t="n"/>
-      <c r="P10" s="12" t="n"/>
+      <c r="P10" s="15" t="inlineStr">
+        <is>
+          <t>7,25 mg P/L</t>
+        </is>
+      </c>
       <c r="Q10" s="12" t="n"/>
-      <c r="R10" s="12" t="n"/>
-      <c r="S10" s="14" t="inlineStr">
+      <c r="R10" s="15" t="inlineStr">
+        <is>
+          <t>14,00 mgNKT/L</t>
+        </is>
+      </c>
+      <c r="S10" s="15" t="inlineStr">
         <is>
           <t>&lt; 0,02 mg O2/L</t>
         </is>
       </c>
-      <c r="T10" s="12" t="n"/>
-      <c r="U10" s="12" t="n"/>
-      <c r="V10" s="12" t="n"/>
-      <c r="W10" s="13" t="inlineStr">
-        <is>
-          <t>0,84 NTU</t>
-        </is>
-      </c>
+      <c r="T10" s="15" t="inlineStr">
+        <is>
+          <t>215,0000 mg/L</t>
+        </is>
+      </c>
+      <c r="U10" s="15" t="inlineStr">
+        <is>
+          <t>138,00 mg/L</t>
+        </is>
+      </c>
+      <c r="V10" s="15" t="inlineStr">
+        <is>
+          <t>102,00 mg/L</t>
+        </is>
+      </c>
+      <c r="W10" s="12" t="n"/>
       <c r="X10" s="13" t="inlineStr">
         <is>
-          <t>6,85 NA</t>
-        </is>
-      </c>
-      <c r="Y10" s="13" t="inlineStr">
-        <is>
-          <t>&lt; 10,00 mg Óleos e Graxas/L</t>
+          <t>5,37 NA</t>
+        </is>
+      </c>
+      <c r="Y10" s="15" t="inlineStr">
+        <is>
+          <t>29,50 mg Óleos e Graxas/L</t>
         </is>
       </c>
     </row>
@@ -9462,44 +9638,117 @@
         </is>
       </c>
       <c r="C11" s="12" t="n"/>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>&lt; 0,02 mg Al/L</t>
-        </is>
-      </c>
+      <c r="D11" s="12" t="n"/>
       <c r="E11" s="12" t="n"/>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>&lt; 0,1 mg Cl/L</t>
-        </is>
-      </c>
+      <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
-      <c r="H11" s="12" t="n"/>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>2,7x10² NMP/100 mL</t>
+        </is>
+      </c>
       <c r="I11" s="12" t="n"/>
-      <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="12" t="n"/>
-      <c r="M11" s="12" t="n"/>
-      <c r="N11" s="12" t="n"/>
+      <c r="J11" s="13" t="inlineStr">
+        <is>
+          <t>&lt; 0,60 mg Pt-Co/L</t>
+        </is>
+      </c>
+      <c r="K11" s="14" t="inlineStr">
+        <is>
+          <t>21,70 mgO2/L</t>
+        </is>
+      </c>
+      <c r="L11" s="15" t="inlineStr">
+        <is>
+          <t>46,00 mg O2/L</t>
+        </is>
+      </c>
+      <c r="M11" s="15" t="inlineStr">
+        <is>
+          <t>2,7x10² NMP/100 mL</t>
+        </is>
+      </c>
+      <c r="N11" s="13" t="inlineStr">
+        <is>
+          <t>0,00 mg Fenol/L</t>
+        </is>
+      </c>
       <c r="O11" s="12" t="n"/>
       <c r="P11" s="12" t="n"/>
-      <c r="Q11" s="15" t="inlineStr">
-        <is>
-          <t>Virtualmente Ausente</t>
-        </is>
-      </c>
+      <c r="Q11" s="12" t="n"/>
       <c r="R11" s="12" t="n"/>
-      <c r="S11" s="13" t="inlineStr">
-        <is>
-          <t>7,00 mg O2/L</t>
+      <c r="S11" s="14" t="inlineStr">
+        <is>
+          <t>&lt; 0,02 mg O2/L</t>
         </is>
       </c>
       <c r="T11" s="12" t="n"/>
       <c r="U11" s="12" t="n"/>
       <c r="V11" s="12" t="n"/>
-      <c r="W11" s="12" t="n"/>
-      <c r="X11" s="12" t="n"/>
-      <c r="Y11" s="12" t="n"/>
+      <c r="W11" s="13" t="inlineStr">
+        <is>
+          <t>0,84 NTU</t>
+        </is>
+      </c>
+      <c r="X11" s="13" t="inlineStr">
+        <is>
+          <t>6,85 NA</t>
+        </is>
+      </c>
+      <c r="Y11" s="13" t="inlineStr">
+        <is>
+          <t>&lt; 10,00 mg Óleos e Graxas/L</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n">
+        <v>46295.60416666666</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Represa 1</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>&lt; 0,02 mg Al/L</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>&lt; 0,1 mg Cl/L</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="n"/>
+      <c r="H12" s="12" t="n"/>
+      <c r="I12" s="12" t="n"/>
+      <c r="J12" s="12" t="n"/>
+      <c r="K12" s="12" t="n"/>
+      <c r="L12" s="12" t="n"/>
+      <c r="M12" s="12" t="n"/>
+      <c r="N12" s="12" t="n"/>
+      <c r="O12" s="12" t="n"/>
+      <c r="P12" s="12" t="n"/>
+      <c r="Q12" s="15" t="inlineStr">
+        <is>
+          <t>Virtualmente Ausente</t>
+        </is>
+      </c>
+      <c r="R12" s="12" t="n"/>
+      <c r="S12" s="13" t="inlineStr">
+        <is>
+          <t>7,00 mg O2/L</t>
+        </is>
+      </c>
+      <c r="T12" s="12" t="n"/>
+      <c r="U12" s="12" t="n"/>
+      <c r="V12" s="12" t="n"/>
+      <c r="W12" s="12" t="n"/>
+      <c r="X12" s="12" t="n"/>
+      <c r="Y12" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9512,13 +9761,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="49" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="90" customWidth="1" min="7" max="7"/>
@@ -9562,7 +9811,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Médio</t>
         </is>
@@ -9599,7 +9848,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Médio</t>
         </is>
@@ -9636,7 +9885,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Médio</t>
         </is>
@@ -9673,7 +9922,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Médio</t>
         </is>
@@ -9710,7 +9959,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Médio</t>
         </is>
@@ -9747,7 +9996,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Médio</t>
         </is>
@@ -9784,7 +10033,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Médio</t>
         </is>
@@ -9821,7 +10070,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Médio</t>
         </is>
@@ -9858,7 +10107,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Médio</t>
         </is>
@@ -9895,7 +10144,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Médio</t>
         </is>
@@ -9932,81 +10181,114 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>Ponto de coleta novo</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>25/08/2026 13:40</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Bomba De Captação De Efluentes - Efluente Bruto</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>1081-1/2026.0</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>'BOMBA DE CAPTAÇÃO DE EFLUENTES - EFLUENTE BRUTO' não está no dicionario.json. Cadastre para padronizar o nome.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Unidade fora do padrão</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>30/09/2026 14:20</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Lagoa 07</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>4220-1/2026.0</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Amônia</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>Unidade 'NH3' não reconhecida (resultado: 6,81 NH3).</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Baixo</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Unidade fora do padrão</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>30/09/2026 14:10</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Lagoa 01</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>4221-1/2026.0</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Amônia</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>Unidade 'NH3' não reconhecida (resultado: 6,81 NH3).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G13"/>
+  <autoFilter ref="A1:G14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10017,7 +10299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -10063,56 +10345,56 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 16:19:28</t>
+          <t>2026-10-20 17:00:01</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>19813-2026 - 1-0.pdf</t>
+          <t>1081-1-2026_0.pdf</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>ERRO</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="n"/>
+          <t>Processado</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>1081-1/2026.0</t>
+        </is>
+      </c>
       <c r="E2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Não parece um laudo Aqualit (texto 'Relatório de Análises' não encontrado). Pode ser um PDF escaneado ou de outro laboratório. — movido para 03_ERROS</t>
+          <t>02_PROCESSADOS\2026\2026-08\2026-08-25_AR_BOMBA-DE-CAPTACAO-DE-EFLUENTES-EFLUENTE-BRUTO_1081-2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-20 14:48:36</t>
+          <t>2026-10-20 16:19:28</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>4296-1-2026_0.pdf</t>
+          <t>19813-2026 - 1-0.pdf</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Processado</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>4296-1/2026.0</t>
-        </is>
-      </c>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_MONTANTE_4296-2026.pdf</t>
+          <t>Não parece um laudo Aqualit (texto 'Relatório de Análises' não encontrado). Pode ser um PDF escaneado ou de outro laboratório. — movido para 03_ERROS</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10406,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>4295-1-2026_0.pdf</t>
+          <t>4296-1-2026_0.pdf</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -10134,15 +10416,15 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>4295-1/2026.0</t>
+          <t>4296-1/2026.0</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_CAPTACAO_4295-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_MONTANTE_4296-2026.pdf</t>
         </is>
       </c>
     </row>
@@ -10154,7 +10436,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>4294-1-2026_0.pdf</t>
+          <t>4295-1-2026_0.pdf</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -10164,15 +10446,15 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>4294-1/2026.0</t>
+          <t>4295-1/2026.0</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_JUSANTE_4294-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_CAPTACAO_4295-2026.pdf</t>
         </is>
       </c>
     </row>
@@ -10184,7 +10466,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>4293-1-2026_0.pdf</t>
+          <t>4294-1-2026_0.pdf</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -10194,7 +10476,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>4293-1/2026.0</t>
+          <t>4294-1/2026.0</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
@@ -10202,7 +10484,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_GOIABAL_4293-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_JUSANTE_4294-2026.pdf</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10496,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>4292-1-2026_0.pdf</t>
+          <t>4293-1-2026_0.pdf</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -10224,7 +10506,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>4292-1/2026.0</t>
+          <t>4293-1/2026.0</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
@@ -10232,7 +10514,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_REPRESA-1_4292-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_GOIABAL_4293-2026.pdf</t>
         </is>
       </c>
     </row>
@@ -10244,7 +10526,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>4291-1-2026_0.pdf</t>
+          <t>4292-1-2026_0.pdf</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -10254,7 +10536,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>4291-1/2026.0</t>
+          <t>4292-1/2026.0</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
@@ -10262,7 +10544,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_SAIDA-DA-MINA_4291-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_REPRESA-1_4292-2026.pdf</t>
         </is>
       </c>
     </row>
@@ -10274,7 +10556,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>4221-1-2026_0.pdf</t>
+          <t>4291-1-2026_0.pdf</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -10284,15 +10566,15 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>4221-1/2026.0</t>
+          <t>4291-1/2026.0</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AR_LAGOA-01_4221-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_SAIDA-DA-MINA_4291-2026.pdf</t>
         </is>
       </c>
     </row>
@@ -10304,7 +10586,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>4220-1-2026_0.pdf</t>
+          <t>4221-1-2026_0.pdf</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -10314,7 +10596,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>4220-1/2026.0</t>
+          <t>4221-1/2026.0</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
@@ -10322,7 +10604,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AR_LAGOA-07_4220-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AR_LAGOA-01_4221-2026.pdf</t>
         </is>
       </c>
     </row>
@@ -10334,7 +10616,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>4219-1-2026_0.pdf</t>
+          <t>4220-1-2026_0.pdf</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -10344,15 +10626,15 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>4219-1/2026.0</t>
+          <t>4220-1/2026.0</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_JUSANTE_4219-2026.pdf</t>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AR_LAGOA-07_4220-2026.pdf</t>
         </is>
       </c>
     </row>
@@ -10364,7 +10646,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>4218-1-2026_0.pdf</t>
+          <t>4219-1-2026_0.pdf</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -10374,7 +10656,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>4218-1/2026.0</t>
+          <t>4219-1/2026.0</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
@@ -10382,12 +10664,42 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
+          <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_JUSANTE_4219-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 14:48:36</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>4218-1-2026_0.pdf</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Processado</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>4218-1/2026.0</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
           <t>02_PROCESSADOS\2026\2026-09\2026-09-30_AB_REPRESA-1_4218-2026.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F12"/>
+  <autoFilter ref="A1:F13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>